--- a/Sevastopol AI База.xlsx
+++ b/Sevastopol AI База.xlsx
@@ -3668,7 +3668,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="0" t="inlineStr">
         <is>
           <t>44.613853, 33.520939</t>
         </is>
@@ -3676,7 +3676,7 @@
       <c r="J45" s="36" t="n"/>
       <c r="K45" s="36" t="n"/>
       <c r="N45" s="37" t="n"/>
-      <c r="O45" t="inlineStr">
+      <c r="O45" s="0" t="inlineStr">
         <is>
           <t>ежедневно 8:00–21:00</t>
         </is>
@@ -3711,7 +3711,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="0" t="inlineStr">
         <is>
           <t>44.602887, 33.523534</t>
         </is>
@@ -3719,7 +3719,7 @@
       <c r="J46" s="36" t="n"/>
       <c r="K46" s="36" t="n"/>
       <c r="N46" s="37" t="n"/>
-      <c r="O46" t="inlineStr">
+      <c r="O46" s="0" t="inlineStr">
         <is>
           <t>ежедневно 8:00–21:00</t>
         </is>
@@ -3754,7 +3754,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="0" t="inlineStr">
         <is>
           <t>44.613565, 33.521972</t>
         </is>
@@ -3762,7 +3762,7 @@
       <c r="J47" s="36" t="n"/>
       <c r="K47" s="36" t="n"/>
       <c r="N47" s="37" t="n"/>
-      <c r="O47" t="inlineStr">
+      <c r="O47" s="0" t="inlineStr">
         <is>
           <t>ежедневно 8:00–21:00</t>
         </is>
@@ -3794,10 +3794,10 @@
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t>Парк Победы</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
+          <t>Победа</t>
+        </is>
+      </c>
+      <c r="H48" s="0" t="inlineStr">
         <is>
           <t>44.592833, 33.551970</t>
         </is>
@@ -3805,7 +3805,7 @@
       <c r="J48" s="36" t="n"/>
       <c r="K48" s="36" t="n"/>
       <c r="N48" s="37" t="n"/>
-      <c r="O48" t="inlineStr">
+      <c r="O48" s="0" t="inlineStr">
         <is>
           <t>ежедневно 8:00–21:00</t>
         </is>
@@ -3840,7 +3840,7 @@
           <t>Остряки (Переход)</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="0" t="inlineStr">
         <is>
           <t>44.574948, 33.520751</t>
         </is>
@@ -3848,7 +3848,7 @@
       <c r="J49" s="36" t="n"/>
       <c r="K49" s="36" t="n"/>
       <c r="N49" s="37" t="n"/>
-      <c r="O49" t="inlineStr">
+      <c r="O49" s="0" t="inlineStr">
         <is>
           <t>ежедневно 8:00–21:00</t>
         </is>
@@ -3884,7 +3884,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="0" t="inlineStr">
         <is>
           <t>44.616897, 33.524675</t>
         </is>
@@ -3922,7 +3922,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="0" t="inlineStr">
         <is>
           <t>44.613956, 33.520455</t>
         </is>
@@ -3930,7 +3930,7 @@
       <c r="J51" s="36" t="n"/>
       <c r="K51" s="36" t="n"/>
       <c r="N51" s="37" t="n"/>
-      <c r="O51" t="inlineStr">
+      <c r="O51" s="0" t="inlineStr">
         <is>
           <t>круглосуточно</t>
         </is>
@@ -4008,7 +4008,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="0" t="inlineStr">
         <is>
           <t>44.612943, 33.521777</t>
         </is>
@@ -4016,7 +4016,7 @@
       <c r="J53" s="36" t="n"/>
       <c r="K53" s="36" t="n"/>
       <c r="N53" s="37" t="n"/>
-      <c r="O53" t="inlineStr">
+      <c r="O53" s="0" t="inlineStr">
         <is>
           <t>ежедневно 8:00–0:00</t>
         </is>
@@ -4051,7 +4051,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="0" t="inlineStr">
         <is>
           <t>44.612459, 33.521029</t>
         </is>
@@ -4059,7 +4059,7 @@
       <c r="J54" s="36" t="n"/>
       <c r="K54" s="36" t="n"/>
       <c r="N54" s="37" t="n"/>
-      <c r="O54" t="inlineStr">
+      <c r="O54" s="0" t="inlineStr">
         <is>
           <t>ежедневно 8:00–0:00</t>
         </is>
@@ -4094,7 +4094,7 @@
           <t>ПОР</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="0" t="inlineStr">
         <is>
           <t>44.590225, 33.460958</t>
         </is>
@@ -4102,7 +4102,7 @@
       <c r="J55" s="36" t="n"/>
       <c r="K55" s="36" t="n"/>
       <c r="N55" s="37" t="n"/>
-      <c r="O55" t="inlineStr">
+      <c r="O55" s="0" t="inlineStr">
         <is>
           <t>ежедневно 8:00–0:00</t>
         </is>
@@ -4137,7 +4137,7 @@
           <t>Омега</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="0" t="inlineStr">
         <is>
           <t>44.589038, 33.434878</t>
         </is>
@@ -4175,7 +4175,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="0" t="inlineStr">
         <is>
           <t>44.607925, 33.507652</t>
         </is>
@@ -4213,7 +4213,7 @@
           <t>Лётчики</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="0" t="inlineStr">
         <is>
           <t>44.597662, 33.462600</t>
         </is>
@@ -4251,7 +4251,7 @@
           <t>Фиолент</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" s="0" t="inlineStr">
         <is>
           <t>44.559088, 33.457345</t>
         </is>
@@ -4289,7 +4289,7 @@
           <t>Стрелка</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H60" s="0" t="inlineStr">
         <is>
           <t>44.587206, 33.485040</t>
         </is>
@@ -4326,7 +4326,7 @@
           <t>Остряки (Переход)</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="0" t="inlineStr">
         <is>
           <t>44.583697, 33.517939</t>
         </is>
@@ -4363,7 +4363,7 @@
           <t>Остряки (Московский)</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H62" s="0" t="inlineStr">
         <is>
           <t>44.552112, 33.529292</t>
         </is>
@@ -4400,7 +4400,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63" s="0" t="inlineStr">
         <is>
           <t>44.613428, 33.518546</t>
         </is>
@@ -4451,7 +4451,7 @@
           <t>+7 (978) 177-82-50</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="O64" s="0" t="inlineStr">
         <is>
           <t>пн–пт 8:00–22:00; сб–вс 9:00–22:00</t>
         </is>
@@ -4529,7 +4529,7 @@
           <t>Омега</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66" s="0" t="inlineStr">
         <is>
           <t>44.585600, 33.466100</t>
         </is>
@@ -4567,7 +4567,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" s="0" t="inlineStr">
         <is>
           <t>44.591980, 33.513005</t>
         </is>
@@ -4605,7 +4605,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H68" s="0" t="inlineStr">
         <is>
           <t>44.606173, 33.520571</t>
         </is>
@@ -4643,7 +4643,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" s="0" t="inlineStr">
         <is>
           <t>44.610599, 33.519576</t>
         </is>
@@ -4681,7 +4681,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H70" s="0" t="inlineStr">
         <is>
           <t>44.617365, 33.522863</t>
         </is>
@@ -4720,7 +4720,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H71" s="0" t="inlineStr">
         <is>
           <t>44.612506, 33.520368</t>
         </is>
@@ -4728,7 +4728,7 @@
       <c r="J71" s="36" t="n"/>
       <c r="K71" s="36" t="n"/>
       <c r="N71" s="37" t="n"/>
-      <c r="O71" t="inlineStr">
+      <c r="O71" s="0" t="inlineStr">
         <is>
           <t>ежедневно 8:00–21:00</t>
         </is>
@@ -4775,7 +4775,7 @@
           <t>+7 (978) 235-10-44</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="O72" s="0" t="inlineStr">
         <is>
           <t>пн–пт 8:30–20:30; сб–вс 9:00–21:00</t>
         </is>
@@ -4822,7 +4822,7 @@
           <t>+7 (978) 274-36-43</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="O73" s="0" t="inlineStr">
         <is>
           <t>ежедневно 9:00–23:00</t>
         </is>
@@ -4857,7 +4857,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H74" s="0" t="inlineStr">
         <is>
           <t>44.614135, 33.523075</t>
         </is>
@@ -4895,7 +4895,7 @@
           <t>Омега</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H75" s="0" t="inlineStr">
         <is>
           <t>44.589576, 33.443540</t>
         </is>
@@ -4933,7 +4933,7 @@
           <t>Остряки</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H76" s="0" t="inlineStr">
         <is>
           <t>44.577755, 33.522742</t>
         </is>
@@ -4941,7 +4941,7 @@
       <c r="J76" s="36" t="n"/>
       <c r="K76" s="36" t="n"/>
       <c r="N76" s="37" t="n"/>
-      <c r="O76" t="inlineStr">
+      <c r="O76" s="0" t="inlineStr">
         <is>
           <t>15:00–23:00</t>
         </is>
@@ -4976,7 +4976,7 @@
           <t>Учкуевка</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H77" s="0" t="inlineStr">
         <is>
           <t>44.645206, 33.537178</t>
         </is>
@@ -4984,7 +4984,7 @@
       <c r="J77" s="36" t="n"/>
       <c r="K77" s="36" t="n"/>
       <c r="N77" s="37" t="n"/>
-      <c r="O77" t="inlineStr">
+      <c r="O77" s="0" t="inlineStr">
         <is>
           <t>10:00–18:00</t>
         </is>
@@ -5019,7 +5019,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H78" s="0" t="inlineStr">
         <is>
           <t>44.609739, 33.520581</t>
         </is>
@@ -5027,7 +5027,7 @@
       <c r="J78" s="36" t="n"/>
       <c r="K78" s="36" t="n"/>
       <c r="N78" s="37" t="n"/>
-      <c r="O78" t="inlineStr">
+      <c r="O78" s="0" t="inlineStr">
         <is>
           <t>9:00–22:00</t>
         </is>
@@ -5062,7 +5062,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H79" s="0" t="inlineStr">
         <is>
           <t>44.605423, 33.522120</t>
         </is>
@@ -5101,7 +5101,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H80" s="0" t="inlineStr">
         <is>
           <t>44.610415, 33.520844</t>
         </is>
@@ -5139,7 +5139,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H81" s="0" t="inlineStr">
         <is>
           <t>44.604480, 33.522839</t>
         </is>
@@ -5178,7 +5178,7 @@
           <t>Симферопольское шоссе</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H82" s="0" t="inlineStr">
         <is>
           <t>44.614676, 33.598989</t>
         </is>
@@ -5216,7 +5216,7 @@
           <t>Балаклава</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H83" s="0" t="inlineStr">
         <is>
           <t>44.516504, 33.594119</t>
         </is>
@@ -5253,7 +5253,7 @@
           <t>Остряки (Московский)</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H84" s="0" t="inlineStr">
         <is>
           <t>44.552112, 33.529292</t>
         </is>
@@ -5291,7 +5291,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H85" s="0" t="inlineStr">
         <is>
           <t>44.602887, 33.523534</t>
         </is>
@@ -5329,7 +5329,7 @@
           <t>Центр</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H86" s="0" t="inlineStr">
         <is>
           <t>44.613428, 33.518546</t>
         </is>
@@ -5339,197 +5339,1071 @@
       <c r="N86" s="37" t="n"/>
     </row>
     <row r="87">
-      <c r="D87" s="35" t="n"/>
+      <c r="A87" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t>Рыбацкий стан</t>
+        </is>
+      </c>
+      <c r="D87" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Легендарный рыбный ресторан в Артбухте, у воды
+✔️ Черноморская кухня: свежий улов, уха, барабуля</t>
+        </is>
+      </c>
       <c r="E87" s="35" t="n"/>
+      <c r="F87" s="0" t="inlineStr">
+        <is>
+          <t>набережная Адмирала Клокачёва, 1</t>
+        </is>
+      </c>
+      <c r="G87" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H87" s="0" t="inlineStr">
+        <is>
+          <t>44.615540, 33.519060</t>
+        </is>
+      </c>
       <c r="J87" s="36" t="n"/>
       <c r="K87" s="36" t="n"/>
-      <c r="N87" s="37" t="n"/>
+      <c r="N87" s="37" t="inlineStr">
+        <is>
+          <t>+7 (8692) 55-72-78</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="D88" s="35" t="n"/>
+      <c r="A88" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C88" s="0" t="inlineStr">
+        <is>
+          <t>Пиратская харчевня</t>
+        </is>
+      </c>
+      <c r="D88" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Ресторан в самом сердце Артбухты
+✔️ Морская кухня, живая музыка, атмосфера пиратской таверны</t>
+        </is>
+      </c>
       <c r="E88" s="35" t="n"/>
+      <c r="F88" s="0" t="inlineStr">
+        <is>
+          <t>набережная Адмирала Клокачёва, 21/3</t>
+        </is>
+      </c>
+      <c r="G88" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H88" s="0" t="inlineStr">
+        <is>
+          <t>44.614083, 33.518264</t>
+        </is>
+      </c>
       <c r="J88" s="36" t="n"/>
       <c r="K88" s="36" t="n"/>
-      <c r="N88" s="37" t="n"/>
+      <c r="N88" s="37" t="inlineStr">
+        <is>
+          <t>+7 (978) 717-47-87</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="D89" s="35" t="n"/>
+      <c r="A89" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C89" s="0" t="inlineStr">
+        <is>
+          <t>Баркас</t>
+        </is>
+      </c>
+      <c r="D89" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Иконический рыбный ресторан у воды
+✔️ Витрина свежего улова: устрицы, барабуля, ставрида, мидии
+✔️ Средиземноморская и европейская кухня, бесплатный Wi-Fi</t>
+        </is>
+      </c>
       <c r="E89" s="35" t="n"/>
+      <c r="F89" s="0" t="inlineStr">
+        <is>
+          <t>Капитанская улица, 2А</t>
+        </is>
+      </c>
+      <c r="G89" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H89" s="0" t="inlineStr">
+        <is>
+          <t>44.614385, 33.514969</t>
+        </is>
+      </c>
       <c r="J89" s="36" t="n"/>
       <c r="K89" s="36" t="n"/>
-      <c r="N89" s="37" t="n"/>
+      <c r="N89" s="37" t="inlineStr">
+        <is>
+          <t>+7 (978) 797-30-52</t>
+        </is>
+      </c>
+      <c r="O89" s="0" t="inlineStr">
+        <is>
+          <t>12:00–1:00</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="D90" s="35" t="n"/>
+      <c r="A90" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C90" s="0" t="inlineStr">
+        <is>
+          <t>BlackSea</t>
+        </is>
+      </c>
+      <c r="D90" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Ресторан здорового питания и современной морской кухни
+✔️ Морепродукты, сезонное меню, трендовая подача</t>
+        </is>
+      </c>
       <c r="E90" s="35" t="n"/>
+      <c r="F90" s="0" t="inlineStr">
+        <is>
+          <t>улица Сенявина, 4</t>
+        </is>
+      </c>
+      <c r="G90" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H90" s="0" t="inlineStr">
+        <is>
+          <t>44.612193, 33.515964</t>
+        </is>
+      </c>
       <c r="J90" s="36" t="n"/>
       <c r="K90" s="36" t="n"/>
-      <c r="N90" s="37" t="n"/>
+      <c r="N90" s="37" t="inlineStr">
+        <is>
+          <t>+7 (978) 788-05-95</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="D91" s="35" t="n"/>
+      <c r="A91" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C91" s="0" t="inlineStr">
+        <is>
+          <t>Il Vino</t>
+        </is>
+      </c>
+      <c r="D91" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Ресторан у воды с видом на бухту
+✔️ Мясо, рыба, десерты, живая музыка</t>
+        </is>
+      </c>
       <c r="E91" s="35" t="n"/>
+      <c r="F91" s="0" t="inlineStr">
+        <is>
+          <t>набережная Адмирала Перелешина, 3</t>
+        </is>
+      </c>
+      <c r="G91" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H91" s="0" t="inlineStr">
+        <is>
+          <t>44.617035, 33.517483</t>
+        </is>
+      </c>
       <c r="J91" s="36" t="n"/>
       <c r="K91" s="36" t="n"/>
       <c r="N91" s="37" t="n"/>
     </row>
     <row r="92">
-      <c r="D92" s="35" t="n"/>
+      <c r="A92" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C92" s="0" t="inlineStr">
+        <is>
+          <t>Гости</t>
+        </is>
+      </c>
+      <c r="D92" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Ресторан в Арт-отеле (Гоголя, 2)
+✔️ Интерьер с картинами, красивая подача блюд</t>
+        </is>
+      </c>
       <c r="E92" s="35" t="n"/>
+      <c r="F92" s="0" t="inlineStr">
+        <is>
+          <t>улица Гоголя, 2</t>
+        </is>
+      </c>
+      <c r="G92" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H92" s="0" t="inlineStr">
+        <is>
+          <t>44.600784, 33.522853</t>
+        </is>
+      </c>
       <c r="J92" s="36" t="n"/>
       <c r="K92" s="36" t="n"/>
       <c r="N92" s="37" t="n"/>
     </row>
     <row r="93">
-      <c r="D93" s="35" t="n"/>
+      <c r="A93" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C93" s="0" t="inlineStr">
+        <is>
+          <t>Старик Хинкалыч</t>
+        </is>
+      </c>
+      <c r="D93" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Грузинская кухня в центре города
+✔️ Хинкали, хачапури, шашлык</t>
+        </is>
+      </c>
       <c r="E93" s="35" t="n"/>
+      <c r="F93" s="0" t="inlineStr">
+        <is>
+          <t>проспект Нахимова, 5</t>
+        </is>
+      </c>
+      <c r="G93" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H93" s="0" t="inlineStr">
+        <is>
+          <t>44.614828, 33.523268</t>
+        </is>
+      </c>
       <c r="J93" s="36" t="n"/>
       <c r="K93" s="36" t="n"/>
       <c r="N93" s="37" t="n"/>
     </row>
     <row r="94">
-      <c r="D94" s="35" t="n"/>
+      <c r="A94" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t>Кочерга</t>
+        </is>
+      </c>
+      <c r="D94" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Семейный ресторан с бизнес-ланчами
+✔️ Большой выбор соусов, уютная обстановка</t>
+        </is>
+      </c>
       <c r="E94" s="35" t="n"/>
+      <c r="F94" s="0" t="inlineStr">
+        <is>
+          <t>улица Народных Ополченцев, 4</t>
+        </is>
+      </c>
+      <c r="G94" s="0" t="inlineStr">
+        <is>
+          <t>Северная</t>
+        </is>
+      </c>
+      <c r="H94" s="0" t="inlineStr">
+        <is>
+          <t>44.629672, 33.538026</t>
+        </is>
+      </c>
       <c r="J94" s="36" t="n"/>
       <c r="K94" s="36" t="n"/>
       <c r="N94" s="37" t="n"/>
     </row>
     <row r="95">
-      <c r="D95" s="35" t="n"/>
+      <c r="A95" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t>Кочерга</t>
+        </is>
+      </c>
+      <c r="D95" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Ресторан авторской кухни на Руднева</t>
+        </is>
+      </c>
       <c r="E95" s="35" t="n"/>
+      <c r="F95" s="0" t="inlineStr">
+        <is>
+          <t>улица Руднева, 39В</t>
+        </is>
+      </c>
+      <c r="G95" s="0" t="inlineStr">
+        <is>
+          <t>Стрелка</t>
+        </is>
+      </c>
+      <c r="H95" s="0" t="inlineStr">
+        <is>
+          <t>44.591253, 33.492209</t>
+        </is>
+      </c>
       <c r="J95" s="36" t="n"/>
       <c r="K95" s="36" t="n"/>
       <c r="N95" s="37" t="n"/>
     </row>
     <row r="96">
-      <c r="D96" s="35" t="n"/>
+      <c r="A96" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t>Гудини</t>
+        </is>
+      </c>
+      <c r="D96" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Ресто-клуб: бранчи, уютный интерьер
+✔️ Детская комната, бар</t>
+        </is>
+      </c>
       <c r="E96" s="35" t="n"/>
+      <c r="F96" s="0" t="inlineStr">
+        <is>
+          <t>улица Маяковского, 9</t>
+        </is>
+      </c>
+      <c r="G96" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H96" s="0" t="inlineStr">
+        <is>
+          <t>44.612564, 33.517910</t>
+        </is>
+      </c>
       <c r="J96" s="36" t="n"/>
       <c r="K96" s="36" t="n"/>
       <c r="N96" s="37" t="n"/>
     </row>
     <row r="97">
-      <c r="D97" s="35" t="n"/>
+      <c r="A97" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>Марани</t>
+        </is>
+      </c>
+      <c r="D97" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Грузинская кухня: хачапури, мясо, овощи гриль
+✔️ Десерты и кофе с собой</t>
+        </is>
+      </c>
       <c r="E97" s="35" t="n"/>
+      <c r="F97" s="0" t="inlineStr">
+        <is>
+          <t>улица Вакуленчука, 33Д</t>
+        </is>
+      </c>
+      <c r="G97" s="0" t="inlineStr">
+        <is>
+          <t>Стрелка</t>
+        </is>
+      </c>
+      <c r="H97" s="0" t="inlineStr">
+        <is>
+          <t>44.587388, 33.478345</t>
+        </is>
+      </c>
       <c r="J97" s="36" t="n"/>
       <c r="K97" s="36" t="n"/>
       <c r="N97" s="37" t="n"/>
     </row>
     <row r="98">
-      <c r="D98" s="35" t="n"/>
+      <c r="A98" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>Loco</t>
+        </is>
+      </c>
+      <c r="D98" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Рестобар: коктейли от бармена, диджей-сеты
+✔️ Удобное расположение в центре</t>
+        </is>
+      </c>
       <c r="E98" s="35" t="n"/>
+      <c r="F98" s="0" t="inlineStr">
+        <is>
+          <t>улица Айвазовского, 3</t>
+        </is>
+      </c>
+      <c r="G98" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H98" s="0" t="inlineStr">
+        <is>
+          <t>44.612672, 33.519996</t>
+        </is>
+      </c>
       <c r="J98" s="36" t="n"/>
       <c r="K98" s="36" t="n"/>
       <c r="N98" s="37" t="n"/>
     </row>
     <row r="99">
-      <c r="D99" s="35" t="n"/>
+      <c r="A99" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>Амбар</t>
+        </is>
+      </c>
+      <c r="D99" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Паб-ресторан с трансляциями футбола
+✔️ Большой экран, пиво и закуски</t>
+        </is>
+      </c>
       <c r="E99" s="35" t="n"/>
+      <c r="F99" s="0" t="inlineStr">
+        <is>
+          <t>проспект Генерала Острякова, 250</t>
+        </is>
+      </c>
+      <c r="G99" s="0" t="inlineStr">
+        <is>
+          <t>Остряки (Московский)</t>
+        </is>
+      </c>
+      <c r="H99" s="0" t="inlineStr">
+        <is>
+          <t>44.553360, 33.529530</t>
+        </is>
+      </c>
       <c r="J99" s="36" t="n"/>
       <c r="K99" s="36" t="n"/>
       <c r="N99" s="37" t="n"/>
     </row>
     <row r="100">
-      <c r="D100" s="35" t="n"/>
+      <c r="A100" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>Юность</t>
+        </is>
+      </c>
+      <c r="D100" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Кафе-ресторан на Хрусталёва
+✔️ Банкеты, поминальные обеды, доставка</t>
+        </is>
+      </c>
       <c r="E100" s="35" t="n"/>
+      <c r="F100" s="0" t="inlineStr">
+        <is>
+          <t>улица Хрусталёва, 33</t>
+        </is>
+      </c>
+      <c r="G100" s="0" t="inlineStr">
+        <is>
+          <t>Остряки</t>
+        </is>
+      </c>
+      <c r="H100" s="0" t="inlineStr">
+        <is>
+          <t>44.579732, 33.513385</t>
+        </is>
+      </c>
       <c r="J100" s="36" t="n"/>
       <c r="K100" s="36" t="n"/>
       <c r="N100" s="37" t="n"/>
     </row>
     <row r="101">
-      <c r="D101" s="35" t="n"/>
+      <c r="A101" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>Етти</t>
+        </is>
+      </c>
+      <c r="D101" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Сеть быстрого питания: вкусные осетинские пирожки
+✔️ Бонусная программа, детское меню</t>
+        </is>
+      </c>
       <c r="E101" s="35" t="n"/>
+      <c r="F101" s="0" t="inlineStr">
+        <is>
+          <t>улица Руднева, 44</t>
+        </is>
+      </c>
+      <c r="G101" s="0" t="inlineStr">
+        <is>
+          <t>Стрелка</t>
+        </is>
+      </c>
+      <c r="H101" s="0" t="inlineStr">
+        <is>
+          <t>44.591770, 33.486634</t>
+        </is>
+      </c>
       <c r="J101" s="36" t="n"/>
       <c r="K101" s="36" t="n"/>
       <c r="N101" s="37" t="n"/>
     </row>
     <row r="102">
-      <c r="D102" s="35" t="n"/>
+      <c r="A102" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t>Мекензи 1783</t>
+        </is>
+      </c>
+      <c r="D102" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Винотека-ресторан на площади Нахимова
+✔️ Вид на море, ужины с вином</t>
+        </is>
+      </c>
       <c r="E102" s="35" t="n"/>
+      <c r="F102" s="0" t="inlineStr">
+        <is>
+          <t>площадь Нахимова, 2</t>
+        </is>
+      </c>
+      <c r="G102" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H102" s="0" t="inlineStr">
+        <is>
+          <t>44.616865, 33.525582</t>
+        </is>
+      </c>
       <c r="J102" s="36" t="n"/>
       <c r="K102" s="36" t="n"/>
       <c r="N102" s="37" t="n"/>
     </row>
     <row r="103">
-      <c r="D103" s="35" t="n"/>
+      <c r="A103" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t>Шашлычная № 1</t>
+        </is>
+      </c>
+      <c r="D103" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Шашлык с доставкой и на вынос
+✔️ Нежное мясо, плотная упаковка, доставка горячим</t>
+        </is>
+      </c>
       <c r="E103" s="35" t="n"/>
+      <c r="F103" s="0" t="inlineStr">
+        <is>
+          <t>проспект Октябрьской Революции, 50В</t>
+        </is>
+      </c>
+      <c r="G103" s="0" t="inlineStr">
+        <is>
+          <t>ПОР</t>
+        </is>
+      </c>
+      <c r="H103" s="0" t="inlineStr">
+        <is>
+          <t>44.585771, 33.470211</t>
+        </is>
+      </c>
       <c r="J103" s="36" t="n"/>
       <c r="K103" s="36" t="n"/>
       <c r="N103" s="37" t="n"/>
     </row>
     <row r="104">
-      <c r="D104" s="35" t="n"/>
+      <c r="A104" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t>Вояж</t>
+        </is>
+      </c>
+      <c r="D104" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Кафе-ресторан с домашней кухней
+✔️ Тихо, есть парковка, можно поработать за кофе</t>
+        </is>
+      </c>
       <c r="E104" s="35" t="n"/>
+      <c r="F104" s="0" t="inlineStr">
+        <is>
+          <t>6-я Бастионная улица, 46</t>
+        </is>
+      </c>
+      <c r="G104" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H104" s="0" t="inlineStr">
+        <is>
+          <t>44.602350, 33.514053</t>
+        </is>
+      </c>
       <c r="J104" s="36" t="n"/>
       <c r="K104" s="36" t="n"/>
       <c r="N104" s="37" t="n"/>
     </row>
     <row r="105">
-      <c r="D105" s="35" t="n"/>
+      <c r="A105" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C105" s="0" t="inlineStr">
+        <is>
+          <t>Ариранг</t>
+        </is>
+      </c>
+      <c r="D105" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Корейская кухня: большие порции
+✔️ Уютный интерьер</t>
+        </is>
+      </c>
       <c r="E105" s="35" t="n"/>
+      <c r="F105" s="0" t="inlineStr">
+        <is>
+          <t>улица Колобова, 37</t>
+        </is>
+      </c>
+      <c r="G105" s="0" t="inlineStr">
+        <is>
+          <t>Омега</t>
+        </is>
+      </c>
+      <c r="H105" s="0" t="inlineStr">
+        <is>
+          <t>44.585846, 33.465684</t>
+        </is>
+      </c>
       <c r="J105" s="36" t="n"/>
       <c r="K105" s="36" t="n"/>
       <c r="N105" s="37" t="n"/>
     </row>
     <row r="106">
-      <c r="D106" s="35" t="n"/>
+      <c r="A106" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
+        <is>
+          <t>Самурай</t>
+        </is>
+      </c>
+      <c r="D106" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Японская кухня и суши на набережной
+✔️ Детская комната, яркий интерьер</t>
+        </is>
+      </c>
       <c r="E106" s="35" t="n"/>
+      <c r="F106" s="0" t="inlineStr">
+        <is>
+          <t>набережная Адмирала Клокачёва, 16</t>
+        </is>
+      </c>
+      <c r="G106" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H106" s="0" t="inlineStr">
+        <is>
+          <t>44.615331, 33.518725</t>
+        </is>
+      </c>
       <c r="J106" s="36" t="n"/>
       <c r="K106" s="36" t="n"/>
       <c r="N106" s="37" t="n"/>
     </row>
     <row r="107">
-      <c r="D107" s="35" t="n"/>
+      <c r="A107" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t>Казбек</t>
+        </is>
+      </c>
+      <c r="D107" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Кавказская кухня на Гоголя
+✔️ Мясо с овощами, домашние лимонады, бизнес-ланчи</t>
+        </is>
+      </c>
       <c r="E107" s="35" t="n"/>
+      <c r="F107" s="0" t="inlineStr">
+        <is>
+          <t>улица Гоголя, 6</t>
+        </is>
+      </c>
+      <c r="G107" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H107" s="0" t="inlineStr">
+        <is>
+          <t>44.599690, 33.521740</t>
+        </is>
+      </c>
       <c r="J107" s="36" t="n"/>
       <c r="K107" s="36" t="n"/>
       <c r="N107" s="37" t="n"/>
     </row>
     <row r="108">
-      <c r="D108" s="35" t="n"/>
+      <c r="A108" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
+        <is>
+          <t>Prince</t>
+        </is>
+      </c>
+      <c r="D108" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Ресторан на набережной Назукина в Балаклаве
+✔️ Назван в честь британского фрегата «Принц»</t>
+        </is>
+      </c>
       <c r="E108" s="35" t="n"/>
+      <c r="F108" s="0" t="inlineStr">
+        <is>
+          <t>Балаклава, набережная Назукина, 1А</t>
+        </is>
+      </c>
+      <c r="G108" s="0" t="inlineStr">
+        <is>
+          <t>Балаклава</t>
+        </is>
+      </c>
+      <c r="H108" s="0" t="inlineStr">
+        <is>
+          <t>44.497255, 33.599402</t>
+        </is>
+      </c>
       <c r="J108" s="36" t="n"/>
       <c r="K108" s="36" t="n"/>
-      <c r="N108" s="37" t="n"/>
+      <c r="N108" s="37" t="inlineStr">
+        <is>
+          <t>+7 (978) 105-58-18</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="D109" s="35" t="n"/>
+      <c r="A109" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C109" s="0" t="inlineStr">
+        <is>
+          <t>УГЛИ</t>
+        </is>
+      </c>
+      <c r="D109" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Кафе-ресторан про еду: мангал, копчение
+✔️ Домашние закрутки из фермерских продуктов
+✔️ Зал для мероприятий, летняя терраса с беседками</t>
+        </is>
+      </c>
       <c r="E109" s="35" t="n"/>
+      <c r="F109" s="0" t="inlineStr">
+        <is>
+          <t>улица Героев Бреста, 21А</t>
+        </is>
+      </c>
+      <c r="G109" s="0" t="inlineStr">
+        <is>
+          <t>Омега</t>
+        </is>
+      </c>
+      <c r="H109" s="0" t="inlineStr">
+        <is>
+          <t>44.582892, 33.446953</t>
+        </is>
+      </c>
       <c r="J109" s="36" t="n"/>
       <c r="K109" s="36" t="n"/>
       <c r="N109" s="37" t="n"/>
+      <c r="O109" s="0" t="inlineStr">
+        <is>
+          <t>11:00–0:00</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="D110" s="35" t="n"/>
+      <c r="A110" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t>Столыпинъ</t>
+        </is>
+      </c>
+      <c r="D110" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Пивная ресторация: пиво, мясо, закуски</t>
+        </is>
+      </c>
       <c r="E110" s="35" t="n"/>
+      <c r="F110" s="0" t="inlineStr">
+        <is>
+          <t>проспект Октябрьской Революции, 24</t>
+        </is>
+      </c>
+      <c r="G110" s="0" t="inlineStr">
+        <is>
+          <t>Лётчики</t>
+        </is>
+      </c>
+      <c r="H110" s="0" t="inlineStr">
+        <is>
+          <t>44.592218, 33.455635</t>
+        </is>
+      </c>
       <c r="J110" s="36" t="n"/>
       <c r="K110" s="36" t="n"/>
-      <c r="N110" s="37" t="n"/>
+      <c r="N110" s="37" t="inlineStr">
+        <is>
+          <t>+7 (8692) 422-319</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="D111" s="35" t="n"/>
+      <c r="A111" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t>Безупречная Чебуречная</t>
+        </is>
+      </c>
+      <c r="D111" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Чебуреки с хрустящей корочкой
+✔️ Атмосфера 90-х, европейская кухня</t>
+        </is>
+      </c>
       <c r="E111" s="35" t="n"/>
+      <c r="F111" s="0" t="inlineStr">
+        <is>
+          <t>Большая Морская, 32</t>
+        </is>
+      </c>
+      <c r="G111" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H111" s="0" t="inlineStr">
+        <is>
+          <t>44.605961, 33.521704</t>
+        </is>
+      </c>
       <c r="J111" s="36" t="n"/>
       <c r="K111" s="36" t="n"/>
       <c r="N111" s="37" t="n"/>
     </row>
     <row r="112">
-      <c r="D112" s="35" t="n"/>
+      <c r="A112" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t>Тбилисити</t>
+        </is>
+      </c>
+      <c r="D112" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Грузинская кухня: хинкали, хачапури, шашлык
+✔️ Семейный формат</t>
+        </is>
+      </c>
       <c r="E112" s="35" t="n"/>
+      <c r="F112" s="0" t="inlineStr">
+        <is>
+          <t>улица Адмирала Фадеева, 48</t>
+        </is>
+      </c>
+      <c r="G112" s="0" t="inlineStr">
+        <is>
+          <t>Лётчики</t>
+        </is>
+      </c>
+      <c r="H112" s="0" t="inlineStr">
+        <is>
+          <t>44.597506, 33.459216</t>
+        </is>
+      </c>
       <c r="J112" s="36" t="n"/>
       <c r="K112" s="36" t="n"/>
       <c r="N112" s="37" t="n"/>
     </row>
     <row r="113">
-      <c r="D113" s="35" t="n"/>
+      <c r="A113" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t>Киото</t>
+        </is>
+      </c>
+      <c r="D113" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Суши-бар с доставкой
+✔️ Роллы, суши, сеты</t>
+        </is>
+      </c>
       <c r="E113" s="35" t="n"/>
+      <c r="F113" s="0" t="inlineStr">
+        <is>
+          <t>улица Руднева, 34</t>
+        </is>
+      </c>
+      <c r="G113" s="0" t="inlineStr">
+        <is>
+          <t>Стрелка</t>
+        </is>
+      </c>
+      <c r="H113" s="0" t="inlineStr">
+        <is>
+          <t>44.591924, 33.491133</t>
+        </is>
+      </c>
       <c r="J113" s="36" t="n"/>
       <c r="K113" s="36" t="n"/>
       <c r="N113" s="37" t="n"/>
     </row>
     <row r="114">
-      <c r="D114" s="35" t="n"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Брискет</t>
+        </is>
+      </c>
+      <c r="D114" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Бургерная/гриль на набережной Парка Победы
+✔️ Сочные бургеры с солёными овощами, быстрый перекус у моря</t>
+        </is>
+      </c>
       <c r="E114" s="35" t="n"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>набережная Парк Победы, 15</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Парк Победы</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>44.608397, 33.455956</t>
+        </is>
+      </c>
       <c r="J114" s="36" t="n"/>
       <c r="K114" s="36" t="n"/>
       <c r="N114" s="37" t="n"/>
@@ -11950,7 +12824,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="25.25" customWidth="1" style="38" min="2" max="2"/>
@@ -12494,6 +13368,290 @@
       <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Яшмовый пляж</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Пляжи</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Пляж «Парк Победы»</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>✔️ Центральный городской пляж с широкой песчаной полосой
+✔️ Развитая инфраструктура: кафе, шезлонги, водные развлечения
+✔️ Рядом одноимённый парк с аллеями</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Парк Победы, западное побережье (ул. Лётчиков)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>44.609259, 33.456871</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Пляжи</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Хрустальный пляж</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>✔️ Городской пляж в центре у мыса Хрустальный
+✔️ Бетонные настилы и купальни, вид на Артбухту
+✔️ Пешком от площади Нахимова</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Мыс Хрустальный, центр</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>44.616908, 33.516735</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Пляжи</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Пляж Учкуевка</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>✔️ Самый популярный песчаный пляж Северной стороны
+✔️ Длинная береговая линия, кафе и набережная
+✔️ Добираться катером из Артбухты или маршруткой</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Учкуевка, Северная сторона</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>44.644258, 33.536515</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Пляжи</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Пляж Любимовка</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>✔️ Широкий песчаный пляж севернее Учкуевки
+✔️ Чистое море, меньше людей, простор</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Любимовка, Северная сторона</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>44.659856, 33.543911</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Пляжи</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Пляж Омега</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>✔️ Песчано-галечный пляж в одноимённой бухте
+✔️ Мелководье — хорошо с детьми, набережная с кафе</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Бухта Омега</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>44.597638, 33.444116</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Пляжи</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Песочный пляж (Песочная бухта)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>✔️ Небольшой уютный пляж в Песочной бухте
+✔️ Песок и пологий вход в воду</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Песочная бухта, Стрелка (ул. Ефремова)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>44.606607, 33.483647</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Пляжи</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Голубая бухта</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>✔️ Дикий пляж с чистейшей водой у входа в Голубую бухту
+✔️ Каменистое дно, прозрачное море, снорклинг</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Голубая бухта, Казачка</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>44.555326, 33.409105</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Пляжи</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Казачья бухта</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>✔️ Пляжи Казачьей бухты: дикие и обустроенные участки
+✔️ Спокойное море, виды на Херсонес</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Казачья бухта</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>44.566952, 33.402615</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Пляжи</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Царский пляж</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>✔️ Один из самых живописных пляжей Фиолента
+✔️ Бирюзовая вода, галька, спуск по лестнице 800 ступеней
+✔️ Вид на Георгиевский монастырь</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Фиолент, под Георгиевским монастырём</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>44.508471, 33.481831</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Пляжи</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Мраморный пляж</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>✔️ Галька светлых пород, прозрачная вода
+✔️ Соседствует с Яшмовым пляжем, подход со стороны Балаклавы и Фиолента</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Между Фиолентом и Балаклавой</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>44.495616, 33.592308</t>
         </is>
       </c>
     </row>

--- a/Sevastopol AI База.xlsx
+++ b/Sevastopol AI База.xlsx
@@ -6372,12 +6372,12 @@
       <c r="N113" s="37" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="0" t="inlineStr">
         <is>
           <t>Рестораны</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="0" t="inlineStr">
         <is>
           <t>Брискет</t>
         </is>
@@ -6389,17 +6389,17 @@
         </is>
       </c>
       <c r="E114" s="35" t="n"/>
-      <c r="F114" t="inlineStr">
+      <c r="F114" s="0" t="inlineStr">
         <is>
           <t>набережная Парк Победы, 15</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="G114" s="0" t="inlineStr">
         <is>
           <t>Парк Победы</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="H114" s="0" t="inlineStr">
         <is>
           <t>44.608397, 33.455956</t>
         </is>
@@ -6409,120 +6409,654 @@
       <c r="N114" s="37" t="n"/>
     </row>
     <row r="115">
-      <c r="D115" s="35" t="n"/>
+      <c r="A115" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>Снежинка</t>
+        </is>
+      </c>
+      <c r="D115" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Арт-кафе в центре: кофе, десерты, завтраки
+✔️ Средний счёт ~1200 ₽</t>
+        </is>
+      </c>
       <c r="E115" s="35" t="n"/>
+      <c r="F115" s="0" t="inlineStr">
+        <is>
+          <t>Большая Морская, 19</t>
+        </is>
+      </c>
+      <c r="G115" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H115" s="0" t="inlineStr">
+        <is>
+          <t>44.606527, 33.522192</t>
+        </is>
+      </c>
       <c r="J115" s="36" t="n"/>
       <c r="K115" s="36" t="n"/>
-      <c r="N115" s="37" t="n"/>
+      <c r="N115" s="37" t="inlineStr">
+        <is>
+          <t>+7 (978) 777-31-81</t>
+        </is>
+      </c>
+      <c r="O115" s="0" t="inlineStr">
+        <is>
+          <t>10:00–22:00</t>
+        </is>
+      </c>
     </row>
     <row r="116">
-      <c r="D116" s="35" t="n"/>
+      <c r="A116" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>Шанхай</t>
+        </is>
+      </c>
+      <c r="D116" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Кафе с восточной кухней
+✔️ Средний счёт ~1000 ₽</t>
+        </is>
+      </c>
       <c r="E116" s="35" t="n"/>
+      <c r="F116" s="0" t="inlineStr">
+        <is>
+          <t>площадь 300-летия Российского Флота, 4/1</t>
+        </is>
+      </c>
+      <c r="G116" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H116" s="0" t="inlineStr">
+        <is>
+          <t>44.613428, 33.518546</t>
+        </is>
+      </c>
       <c r="J116" s="36" t="n"/>
       <c r="K116" s="36" t="n"/>
       <c r="N116" s="37" t="n"/>
+      <c r="O116" s="0" t="inlineStr">
+        <is>
+          <t>11:00–0:00</t>
+        </is>
+      </c>
     </row>
     <row r="117">
-      <c r="D117" s="35" t="n"/>
+      <c r="A117" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t>Миска</t>
+        </is>
+      </c>
+      <c r="D117" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Кафе с домашней едой и боулами
+✔️ Средний счёт ~700 ₽</t>
+        </is>
+      </c>
       <c r="E117" s="35" t="n"/>
+      <c r="F117" s="0" t="inlineStr">
+        <is>
+          <t>Портовая улица, 17</t>
+        </is>
+      </c>
+      <c r="G117" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H117" s="0" t="inlineStr">
+        <is>
+          <t>44.597345, 33.527468</t>
+        </is>
+      </c>
       <c r="J117" s="36" t="n"/>
       <c r="K117" s="36" t="n"/>
       <c r="N117" s="37" t="n"/>
+      <c r="O117" s="0" t="inlineStr">
+        <is>
+          <t>11:00–21:00</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="D118" s="35" t="n"/>
+      <c r="A118" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C118" s="0" t="inlineStr">
+        <is>
+          <t>The Угол</t>
+        </is>
+      </c>
+      <c r="D118" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Кафе в центре: завтраки, сэндвичи, кофе
+✔️ Средний счёт ~1500 ₽</t>
+        </is>
+      </c>
       <c r="E118" s="35" t="n"/>
+      <c r="F118" s="0" t="inlineStr">
+        <is>
+          <t>улица Маяковского, 5</t>
+        </is>
+      </c>
+      <c r="G118" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H118" s="0" t="inlineStr">
+        <is>
+          <t>44.612278, 33.518675</t>
+        </is>
+      </c>
       <c r="J118" s="36" t="n"/>
       <c r="K118" s="36" t="n"/>
       <c r="N118" s="37" t="n"/>
+      <c r="O118" s="0" t="inlineStr">
+        <is>
+          <t>10:00–22:00</t>
+        </is>
+      </c>
     </row>
     <row r="119">
-      <c r="D119" s="35" t="n"/>
+      <c r="A119" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t>Челентано</t>
+        </is>
+      </c>
+      <c r="D119" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Пиццерия на площади 300-летия
+✔️ Летняя терраса, игровая зона для детей с батутом</t>
+        </is>
+      </c>
       <c r="E119" s="35" t="n"/>
+      <c r="F119" s="0" t="inlineStr">
+        <is>
+          <t>площадь 300-летия Российского Флота, 1</t>
+        </is>
+      </c>
+      <c r="G119" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H119" s="0" t="inlineStr">
+        <is>
+          <t>44.613637, 33.518395</t>
+        </is>
+      </c>
       <c r="J119" s="36" t="n"/>
       <c r="K119" s="36" t="n"/>
       <c r="N119" s="37" t="n"/>
     </row>
     <row r="120">
-      <c r="D120" s="35" t="n"/>
+      <c r="A120" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t>Пиватека</t>
+        </is>
+      </c>
+      <c r="D120" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Пивное кафе с местным разливным пивом
+✔️ Закуски: гренки, орешки, мясные сеты</t>
+        </is>
+      </c>
       <c r="E120" s="35" t="n"/>
+      <c r="F120" s="0" t="inlineStr">
+        <is>
+          <t>улица Адмирала Октябрьского, 3</t>
+        </is>
+      </c>
+      <c r="G120" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H120" s="0" t="inlineStr">
+        <is>
+          <t>44.603302, 33.521955</t>
+        </is>
+      </c>
       <c r="J120" s="36" t="n"/>
       <c r="K120" s="36" t="n"/>
       <c r="N120" s="37" t="n"/>
     </row>
     <row r="121">
-      <c r="D121" s="35" t="n"/>
+      <c r="A121" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C121" s="0" t="inlineStr">
+        <is>
+          <t>Имбирь</t>
+        </is>
+      </c>
+      <c r="D121" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Суши-бар: роллы, суши, необычные сочетания
+✔️ Доставка</t>
+        </is>
+      </c>
       <c r="E121" s="35" t="n"/>
+      <c r="F121" s="0" t="inlineStr">
+        <is>
+          <t>проспект Победы, 44/2</t>
+        </is>
+      </c>
+      <c r="G121" s="0" t="inlineStr">
+        <is>
+          <t>Победа</t>
+        </is>
+      </c>
+      <c r="H121" s="0" t="inlineStr">
+        <is>
+          <t>44.590926, 33.556443</t>
+        </is>
+      </c>
       <c r="J121" s="36" t="n"/>
       <c r="K121" s="36" t="n"/>
       <c r="N121" s="37" t="n"/>
     </row>
     <row r="122">
-      <c r="D122" s="35" t="n"/>
+      <c r="A122" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t>Кур Крыло</t>
+        </is>
+      </c>
+      <c r="D122" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Курица на гриле: крылышки Бафало, ножки
+✔️ Доставка, оплата картой</t>
+        </is>
+      </c>
       <c r="E122" s="35" t="n"/>
+      <c r="F122" s="0" t="inlineStr">
+        <is>
+          <t>проспект Октябрьской Революции, 32Г</t>
+        </is>
+      </c>
+      <c r="G122" s="0" t="inlineStr">
+        <is>
+          <t>ПОР</t>
+        </is>
+      </c>
+      <c r="H122" s="0" t="inlineStr">
+        <is>
+          <t>44.585771, 33.470211</t>
+        </is>
+      </c>
       <c r="J122" s="36" t="n"/>
       <c r="K122" s="36" t="n"/>
       <c r="N122" s="37" t="n"/>
     </row>
     <row r="123">
-      <c r="D123" s="35" t="n"/>
+      <c r="A123" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t>Самса</t>
+        </is>
+      </c>
+      <c r="D123" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Восточный фастфуд: самса, люля-кебаб из баранины
+✔️ Современный интерьер, быстрое обслуживание</t>
+        </is>
+      </c>
       <c r="E123" s="35" t="n"/>
+      <c r="F123" s="0" t="inlineStr">
+        <is>
+          <t>улица Шабалина, 42А</t>
+        </is>
+      </c>
+      <c r="G123" s="0" t="inlineStr">
+        <is>
+          <t>Остряки</t>
+        </is>
+      </c>
+      <c r="H123" s="0" t="inlineStr">
+        <is>
+          <t>44.571459, 33.495671</t>
+        </is>
+      </c>
       <c r="J123" s="36" t="n"/>
       <c r="K123" s="36" t="n"/>
       <c r="N123" s="37" t="n"/>
     </row>
     <row r="124">
-      <c r="D124" s="35" t="n"/>
+      <c r="A124" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C124" s="0" t="inlineStr">
+        <is>
+          <t>Суши-Store</t>
+        </is>
+      </c>
+      <c r="D124" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Суши и роллы в ТЦ «Ниагара»
+✔️ Приятные цены, кофе с собой</t>
+        </is>
+      </c>
       <c r="E124" s="35" t="n"/>
+      <c r="F124" s="0" t="inlineStr">
+        <is>
+          <t>улица Вакуленчука, 20</t>
+        </is>
+      </c>
+      <c r="G124" s="0" t="inlineStr">
+        <is>
+          <t>Стрелка</t>
+        </is>
+      </c>
+      <c r="H124" s="0" t="inlineStr">
+        <is>
+          <t>44.592581, 33.485432</t>
+        </is>
+      </c>
       <c r="J124" s="36" t="n"/>
       <c r="K124" s="36" t="n"/>
       <c r="N124" s="37" t="n"/>
     </row>
     <row r="125">
-      <c r="D125" s="35" t="n"/>
+      <c r="A125" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C125" s="0" t="inlineStr">
+        <is>
+          <t>Сан-Тай</t>
+        </is>
+      </c>
+      <c r="D125" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Суши-кафе: роллы, том-ям
+✔️ Бизнес-ланчи</t>
+        </is>
+      </c>
       <c r="E125" s="35" t="n"/>
+      <c r="F125" s="0" t="inlineStr">
+        <is>
+          <t>проспект Генерала Острякова, 64</t>
+        </is>
+      </c>
+      <c r="G125" s="0" t="inlineStr">
+        <is>
+          <t>Остряки</t>
+        </is>
+      </c>
+      <c r="H125" s="0" t="inlineStr">
+        <is>
+          <t>44.579256, 33.518323</t>
+        </is>
+      </c>
       <c r="J125" s="36" t="n"/>
       <c r="K125" s="36" t="n"/>
       <c r="N125" s="37" t="n"/>
     </row>
     <row r="126">
-      <c r="D126" s="35" t="n"/>
+      <c r="A126" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C126" s="0" t="inlineStr">
+        <is>
+          <t>Пар и Дым</t>
+        </is>
+      </c>
+      <c r="D126" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Антикафе с русской парной: баня, сауна
+✔️ Можно приносить свою еду</t>
+        </is>
+      </c>
       <c r="E126" s="35" t="n"/>
+      <c r="F126" s="0" t="inlineStr">
+        <is>
+          <t>улица Токарева, 2Б</t>
+        </is>
+      </c>
+      <c r="G126" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H126" s="0" t="inlineStr">
+        <is>
+          <t>44.587598, 33.501830</t>
+        </is>
+      </c>
       <c r="J126" s="36" t="n"/>
       <c r="K126" s="36" t="n"/>
       <c r="N126" s="37" t="n"/>
     </row>
     <row r="127">
-      <c r="D127" s="35" t="n"/>
+      <c r="A127" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C127" s="0" t="inlineStr">
+        <is>
+          <t>Макао</t>
+        </is>
+      </c>
+      <c r="D127" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Кальян-бар с паб-меню
+✔️ Стильный дизайн, коктейли</t>
+        </is>
+      </c>
       <c r="E127" s="35" t="n"/>
+      <c r="F127" s="0" t="inlineStr">
+        <is>
+          <t>улица Героев Бреста, 57</t>
+        </is>
+      </c>
+      <c r="G127" s="0" t="inlineStr">
+        <is>
+          <t>Омега</t>
+        </is>
+      </c>
+      <c r="H127" s="0" t="inlineStr">
+        <is>
+          <t>44.591785, 33.448398</t>
+        </is>
+      </c>
       <c r="J127" s="36" t="n"/>
       <c r="K127" s="36" t="n"/>
       <c r="N127" s="37" t="n"/>
     </row>
     <row r="128">
-      <c r="D128" s="35" t="n"/>
+      <c r="A128" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t>Goodwood</t>
+        </is>
+      </c>
+      <c r="D128" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Лаунж-кафе с коктейлями и вечеринками
+✔️ Уютная атмосфера, дискотеки по выходным</t>
+        </is>
+      </c>
       <c r="E128" s="35" t="n"/>
+      <c r="F128" s="0" t="inlineStr">
+        <is>
+          <t>проспект Октябрьской Революции, 61</t>
+        </is>
+      </c>
+      <c r="G128" s="0" t="inlineStr">
+        <is>
+          <t>Лётчики</t>
+        </is>
+      </c>
+      <c r="H128" s="0" t="inlineStr">
+        <is>
+          <t>44.589895, 33.461829</t>
+        </is>
+      </c>
       <c r="J128" s="36" t="n"/>
       <c r="K128" s="36" t="n"/>
       <c r="N128" s="37" t="n"/>
     </row>
     <row r="129">
-      <c r="D129" s="35" t="n"/>
+      <c r="A129" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C129" s="0" t="inlineStr">
+        <is>
+          <t>Ёжики</t>
+        </is>
+      </c>
+      <c r="D129" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Кафе-кондитерская: торты и пирожные
+✔️ Можно поработать, встретиться с друзьями</t>
+        </is>
+      </c>
       <c r="E129" s="35" t="n"/>
+      <c r="F129" s="0" t="inlineStr">
+        <is>
+          <t>проспект Генерала Острякова, 225Б</t>
+        </is>
+      </c>
+      <c r="G129" s="0" t="inlineStr">
+        <is>
+          <t>Остряки</t>
+        </is>
+      </c>
+      <c r="H129" s="0" t="inlineStr">
+        <is>
+          <t>44.556299, 33.529375</t>
+        </is>
+      </c>
       <c r="J129" s="36" t="n"/>
       <c r="K129" s="36" t="n"/>
       <c r="N129" s="37" t="n"/>
     </row>
     <row r="130">
-      <c r="D130" s="35" t="n"/>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Кондитерские</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Медоборы</t>
+        </is>
+      </c>
+      <c r="D130" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Сеть кондитерских: торты, пирожные, выпечка
+✔️ Торт «Ай-Петри», свежие десерты к чаю</t>
+        </is>
+      </c>
       <c r="E130" s="35" t="n"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>улица Адмирала Октябрьского, 20</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>44.602421, 33.516187</t>
+        </is>
+      </c>
       <c r="J130" s="36" t="n"/>
       <c r="K130" s="36" t="n"/>
       <c r="N130" s="37" t="n"/>
     </row>
     <row r="131">
-      <c r="D131" s="35" t="n"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Кондитерские</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Медоборы</t>
+        </is>
+      </c>
+      <c r="D131" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Кондитерская на Октябрьской Революции
+✔️ Торты и пирожные собственного производства</t>
+        </is>
+      </c>
       <c r="E131" s="35" t="n"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>проспект Октябрьской Революции, 57А</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>ПОР</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>44.590225, 33.460958</t>
+        </is>
+      </c>
       <c r="J131" s="36" t="n"/>
       <c r="K131" s="36" t="n"/>
       <c r="N131" s="37" t="n"/>
@@ -13372,284 +13906,284 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>Пляжи</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>Пляж «Парк Победы»</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>✔️ Центральный городской пляж с широкой песчаной полосой
 ✔️ Развитая инфраструктура: кафе, шезлонги, водные развлечения
 ✔️ Рядом одноимённый парк с аллеями</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>Парк Победы, западное побережье (ул. Лётчиков)</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>44.609259, 33.456871</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>Пляжи</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>Хрустальный пляж</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>✔️ Городской пляж в центре у мыса Хрустальный
 ✔️ Бетонные настилы и купальни, вид на Артбухту
 ✔️ Пешком от площади Нахимова</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>Мыс Хрустальный, центр</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>44.616908, 33.516735</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>Пляжи</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>Пляж Учкуевка</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>✔️ Самый популярный песчаный пляж Северной стороны
 ✔️ Длинная береговая линия, кафе и набережная
 ✔️ Добираться катером из Артбухты или маршруткой</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>Учкуевка, Северная сторона</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>44.644258, 33.536515</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>Пляжи</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>Пляж Любимовка</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>✔️ Широкий песчаный пляж севернее Учкуевки
 ✔️ Чистое море, меньше людей, простор</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>Любимовка, Северная сторона</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>44.659856, 33.543911</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>Пляжи</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>Пляж Омега</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>✔️ Песчано-галечный пляж в одноимённой бухте
 ✔️ Мелководье — хорошо с детьми, набережная с кафе</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>Бухта Омега</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>44.597638, 33.444116</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>Пляжи</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>Песочный пляж (Песочная бухта)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>✔️ Небольшой уютный пляж в Песочной бухте
 ✔️ Песок и пологий вход в воду</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>Песочная бухта, Стрелка (ул. Ефремова)</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>44.606607, 33.483647</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>Пляжи</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>Голубая бухта</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>✔️ Дикий пляж с чистейшей водой у входа в Голубую бухту
 ✔️ Каменистое дно, прозрачное море, снорклинг</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>Голубая бухта, Казачка</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>44.555326, 33.409105</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>Пляжи</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>Казачья бухта</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>✔️ Пляжи Казачьей бухты: дикие и обустроенные участки
 ✔️ Спокойное море, виды на Херсонес</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>Казачья бухта</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="0" t="inlineStr">
         <is>
           <t>44.566952, 33.402615</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>Пляжи</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>Царский пляж</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>✔️ Один из самых живописных пляжей Фиолента
 ✔️ Бирюзовая вода, галька, спуск по лестнице 800 ступеней
 ✔️ Вид на Георгиевский монастырь</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>Фиолент, под Георгиевским монастырём</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t>44.508471, 33.481831</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>Пляжи</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>Мраморный пляж</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>✔️ Галька светлых пород, прозрачная вода
 ✔️ Соседствует с Яшмовым пляжем, подход со стороны Балаклавы и Фиолента</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
         <is>
           <t>Между Фиолентом и Балаклавой</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="0" t="inlineStr">
         <is>
           <t>44.495616, 33.592308</t>
         </is>

--- a/Sevastopol AI База.xlsx
+++ b/Sevastopol AI База.xlsx
@@ -6988,12 +6988,12 @@
       <c r="N129" s="37" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="0" t="inlineStr">
         <is>
           <t>Кондитерские</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C130" s="0" t="inlineStr">
         <is>
           <t>Медоборы</t>
         </is>
@@ -7005,17 +7005,17 @@
         </is>
       </c>
       <c r="E130" s="35" t="n"/>
-      <c r="F130" t="inlineStr">
+      <c r="F130" s="0" t="inlineStr">
         <is>
           <t>улица Адмирала Октябрьского, 20</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="G130" s="0" t="inlineStr">
         <is>
           <t>Центр</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="H130" s="0" t="inlineStr">
         <is>
           <t>44.602421, 33.516187</t>
         </is>
@@ -7025,12 +7025,12 @@
       <c r="N130" s="37" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="0" t="inlineStr">
         <is>
           <t>Кондитерские</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C131" s="0" t="inlineStr">
         <is>
           <t>Медоборы</t>
         </is>
@@ -7042,17 +7042,17 @@
         </is>
       </c>
       <c r="E131" s="35" t="n"/>
-      <c r="F131" t="inlineStr">
+      <c r="F131" s="0" t="inlineStr">
         <is>
           <t>проспект Октябрьской Революции, 57А</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G131" s="0" t="inlineStr">
         <is>
           <t>ПОР</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="H131" s="0" t="inlineStr">
         <is>
           <t>44.590225, 33.460958</t>
         </is>
@@ -7062,204 +7062,1218 @@
       <c r="N131" s="37" t="n"/>
     </row>
     <row r="132">
-      <c r="D132" s="35" t="n"/>
+      <c r="A132" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="B132" s="0" t="inlineStr">
+        <is>
+          <t>Бары и пабы</t>
+        </is>
+      </c>
+      <c r="C132" s="0" t="inlineStr">
+        <is>
+          <t>Барабуля Бар</t>
+        </is>
+      </c>
+      <c r="D132" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Морской бар-кафе в центре
+✔️ Рыба, морепродукты, крафт и коктейли</t>
+        </is>
+      </c>
       <c r="E132" s="35" t="n"/>
+      <c r="F132" s="0" t="inlineStr">
+        <is>
+          <t>Большая Морская, 43</t>
+        </is>
+      </c>
+      <c r="G132" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H132" s="0" t="inlineStr">
+        <is>
+          <t>44.602206, 33.523755</t>
+        </is>
+      </c>
       <c r="J132" s="36" t="n"/>
       <c r="K132" s="36" t="n"/>
-      <c r="N132" s="37" t="n"/>
+      <c r="N132" s="37" t="inlineStr">
+        <is>
+          <t>+7 (978) 106-61-45</t>
+        </is>
+      </c>
     </row>
     <row r="133">
-      <c r="D133" s="35" t="n"/>
+      <c r="A133" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="B133" s="0" t="inlineStr">
+        <is>
+          <t>Бары и пабы</t>
+        </is>
+      </c>
+      <c r="C133" s="0" t="inlineStr">
+        <is>
+          <t>45 Параллель</t>
+        </is>
+      </c>
+      <c r="D133" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Ресторан-бар на проспекте Нахимова
+✔️ Морская кухня, семейные обеды</t>
+        </is>
+      </c>
       <c r="E133" s="35" t="n"/>
+      <c r="F133" s="0" t="inlineStr">
+        <is>
+          <t>проспект Нахимова, 5А</t>
+        </is>
+      </c>
+      <c r="G133" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H133" s="0" t="inlineStr">
+        <is>
+          <t>44.613565, 33.521972</t>
+        </is>
+      </c>
       <c r="J133" s="36" t="n"/>
       <c r="K133" s="36" t="n"/>
-      <c r="N133" s="37" t="n"/>
+      <c r="N133" s="37" t="inlineStr">
+        <is>
+          <t>+7 (978) 112-15-65</t>
+        </is>
+      </c>
+      <c r="O133" s="0" t="inlineStr">
+        <is>
+          <t>ежедневно 9:00–23:00</t>
+        </is>
+      </c>
     </row>
     <row r="134">
-      <c r="D134" s="35" t="n"/>
+      <c r="A134" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="B134" s="0" t="inlineStr">
+        <is>
+          <t>Бары и пабы</t>
+        </is>
+      </c>
+      <c r="C134" s="0" t="inlineStr">
+        <is>
+          <t>Пиворотти</t>
+        </is>
+      </c>
+      <c r="D134" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Пивной бар на набережной Корнилова
+✔️ Работает 24/7</t>
+        </is>
+      </c>
       <c r="E134" s="35" t="n"/>
+      <c r="F134" s="0" t="inlineStr">
+        <is>
+          <t>набережная Корнилова, 9</t>
+        </is>
+      </c>
+      <c r="G134" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H134" s="0" t="inlineStr">
+        <is>
+          <t>44.612902, 33.518974</t>
+        </is>
+      </c>
       <c r="J134" s="36" t="n"/>
       <c r="K134" s="36" t="n"/>
       <c r="N134" s="37" t="n"/>
+      <c r="O134" s="0" t="inlineStr">
+        <is>
+          <t>круглосуточно</t>
+        </is>
+      </c>
     </row>
     <row r="135">
-      <c r="D135" s="35" t="n"/>
+      <c r="A135" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="B135" s="0" t="inlineStr">
+        <is>
+          <t>Бары и пабы</t>
+        </is>
+      </c>
+      <c r="C135" s="0" t="inlineStr">
+        <is>
+          <t>BeerLoga</t>
+        </is>
+      </c>
+      <c r="D135" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Пивной паб на Остряках
+✔️ Работает 24/7</t>
+        </is>
+      </c>
       <c r="E135" s="35" t="n"/>
+      <c r="F135" s="0" t="inlineStr">
+        <is>
+          <t>улица Николая Музыки, 52</t>
+        </is>
+      </c>
+      <c r="G135" s="0" t="inlineStr">
+        <is>
+          <t>Остряки</t>
+        </is>
+      </c>
+      <c r="H135" s="0" t="inlineStr">
+        <is>
+          <t>44.584177, 33.522021</t>
+        </is>
+      </c>
       <c r="J135" s="36" t="n"/>
       <c r="K135" s="36" t="n"/>
       <c r="N135" s="37" t="n"/>
+      <c r="O135" s="0" t="inlineStr">
+        <is>
+          <t>круглосуточно</t>
+        </is>
+      </c>
     </row>
     <row r="136">
-      <c r="D136" s="35" t="n"/>
+      <c r="A136" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="B136" s="0" t="inlineStr">
+        <is>
+          <t>Бары и пабы</t>
+        </is>
+      </c>
+      <c r="C136" s="0" t="inlineStr">
+        <is>
+          <t>Атака</t>
+        </is>
+      </c>
+      <c r="D136" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Бар на Вакуленчука
+✔️ Коктейли, закуски, трансляции</t>
+        </is>
+      </c>
       <c r="E136" s="35" t="n"/>
+      <c r="F136" s="0" t="inlineStr">
+        <is>
+          <t>улица Вакуленчука, 36/1</t>
+        </is>
+      </c>
+      <c r="G136" s="0" t="inlineStr">
+        <is>
+          <t>Стрелка</t>
+        </is>
+      </c>
+      <c r="H136" s="0" t="inlineStr">
+        <is>
+          <t>44.588137, 33.478697</t>
+        </is>
+      </c>
       <c r="J136" s="36" t="n"/>
       <c r="K136" s="36" t="n"/>
       <c r="N136" s="37" t="n"/>
     </row>
     <row r="137">
-      <c r="D137" s="35" t="n"/>
+      <c r="A137" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="B137" s="0" t="inlineStr">
+        <is>
+          <t>Бары и пабы</t>
+        </is>
+      </c>
+      <c r="C137" s="0" t="inlineStr">
+        <is>
+          <t>Тот ещё бар</t>
+        </is>
+      </c>
+      <c r="D137" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Бар на Октябрьской Революции
+✔️ Коктейли и закуски</t>
+        </is>
+      </c>
       <c r="E137" s="35" t="n"/>
+      <c r="F137" s="0" t="inlineStr">
+        <is>
+          <t>проспект Октябрьской Революции, 50</t>
+        </is>
+      </c>
+      <c r="G137" s="0" t="inlineStr">
+        <is>
+          <t>Лётчики</t>
+        </is>
+      </c>
+      <c r="H137" s="0" t="inlineStr">
+        <is>
+          <t>44.587760, 33.460106</t>
+        </is>
+      </c>
       <c r="J137" s="36" t="n"/>
       <c r="K137" s="36" t="n"/>
       <c r="N137" s="37" t="n"/>
     </row>
     <row r="138">
-      <c r="D138" s="35" t="n"/>
+      <c r="A138" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="B138" s="0" t="inlineStr">
+        <is>
+          <t>Бары и пабы</t>
+        </is>
+      </c>
+      <c r="C138" s="0" t="inlineStr">
+        <is>
+          <t>Меркурий</t>
+        </is>
+      </c>
+      <c r="D138" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Паб на Гоголя: бизнес-ланчи, Wi-Fi
+✔️ Второй бар «Меркурий» — на Матросском бульваре</t>
+        </is>
+      </c>
       <c r="E138" s="35" t="n"/>
+      <c r="F138" s="0" t="inlineStr">
+        <is>
+          <t>улица Гоголя, 28</t>
+        </is>
+      </c>
+      <c r="G138" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H138" s="0" t="inlineStr">
+        <is>
+          <t>44.592150, 33.516826</t>
+        </is>
+      </c>
       <c r="J138" s="36" t="n"/>
       <c r="K138" s="36" t="n"/>
       <c r="N138" s="37" t="n"/>
     </row>
     <row r="139">
-      <c r="D139" s="35" t="n"/>
+      <c r="A139" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="B139" s="0" t="inlineStr">
+        <is>
+          <t>Бары и пабы</t>
+        </is>
+      </c>
+      <c r="C139" s="0" t="inlineStr">
+        <is>
+          <t>Амбар Пицца</t>
+        </is>
+      </c>
+      <c r="D139" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Пивной бар с пиццей на Колобова
+✔️ Разливное пиво, закуски к пиву</t>
+        </is>
+      </c>
       <c r="E139" s="35" t="n"/>
+      <c r="F139" s="0" t="inlineStr">
+        <is>
+          <t>улица Колобова, 34/1</t>
+        </is>
+      </c>
+      <c r="G139" s="0" t="inlineStr">
+        <is>
+          <t>Омега</t>
+        </is>
+      </c>
+      <c r="H139" s="0" t="inlineStr">
+        <is>
+          <t>44.585022, 33.466243</t>
+        </is>
+      </c>
       <c r="J139" s="36" t="n"/>
       <c r="K139" s="36" t="n"/>
       <c r="N139" s="37" t="n"/>
     </row>
     <row r="140">
-      <c r="D140" s="35" t="n"/>
+      <c r="A140" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="B140" s="0" t="inlineStr">
+        <is>
+          <t>Бары и пабы</t>
+        </is>
+      </c>
+      <c r="C140" s="0" t="inlineStr">
+        <is>
+          <t>NeFigase</t>
+        </is>
+      </c>
+      <c r="D140" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Паб с караоке и летней верандой
+✔️ Мидии, суши, коктейли</t>
+        </is>
+      </c>
       <c r="E140" s="35" t="n"/>
+      <c r="F140" s="0" t="inlineStr">
+        <is>
+          <t>проспект Генерала Острякова, 158А</t>
+        </is>
+      </c>
+      <c r="G140" s="0" t="inlineStr">
+        <is>
+          <t>Остряки</t>
+        </is>
+      </c>
+      <c r="H140" s="0" t="inlineStr">
+        <is>
+          <t>44.564776, 33.524184</t>
+        </is>
+      </c>
       <c r="J140" s="36" t="n"/>
       <c r="K140" s="36" t="n"/>
       <c r="N140" s="37" t="n"/>
     </row>
     <row r="141">
-      <c r="D141" s="35" t="n"/>
+      <c r="A141" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="B141" s="0" t="inlineStr">
+        <is>
+          <t>Бары и пабы</t>
+        </is>
+      </c>
+      <c r="C141" s="0" t="inlineStr">
+        <is>
+          <t>Бар тяжёлого рока</t>
+        </is>
+      </c>
+      <c r="D141" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Рок-бар на Хрюкина
+✔️ Тяжёлая музыка, пиво, закуски</t>
+        </is>
+      </c>
       <c r="E141" s="35" t="n"/>
+      <c r="F141" s="0" t="inlineStr">
+        <is>
+          <t>улица Генерала Хрюкина, 1А</t>
+        </is>
+      </c>
+      <c r="G141" s="0" t="inlineStr">
+        <is>
+          <t>Остряки (Хрюкина)</t>
+        </is>
+      </c>
+      <c r="H141" s="0" t="inlineStr">
+        <is>
+          <t>44.567503, 33.525704</t>
+        </is>
+      </c>
       <c r="J141" s="36" t="n"/>
       <c r="K141" s="36" t="n"/>
       <c r="N141" s="37" t="n"/>
+      <c r="O141" s="0" t="inlineStr">
+        <is>
+          <t>14:00–1:00</t>
+        </is>
+      </c>
     </row>
     <row r="142">
-      <c r="D142" s="35" t="n"/>
+      <c r="A142" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="B142" s="0" t="inlineStr">
+        <is>
+          <t>Фастфуд</t>
+        </is>
+      </c>
+      <c r="C142" s="0" t="inlineStr">
+        <is>
+          <t>Супертяж</t>
+        </is>
+      </c>
+      <c r="D142" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Шаурма, фастфуд и кофе на Хрюкина
+✔️ Картошка фри, наггетсы, бодрая атмосфера</t>
+        </is>
+      </c>
       <c r="E142" s="35" t="n"/>
+      <c r="F142" s="0" t="inlineStr">
+        <is>
+          <t>проспект Генерала Острякова, 135</t>
+        </is>
+      </c>
+      <c r="G142" s="0" t="inlineStr">
+        <is>
+          <t>Остряки (Хрюкина)</t>
+        </is>
+      </c>
+      <c r="H142" s="0" t="inlineStr">
+        <is>
+          <t>44.566167, 33.524623</t>
+        </is>
+      </c>
       <c r="J142" s="36" t="n"/>
       <c r="K142" s="36" t="n"/>
       <c r="N142" s="37" t="n"/>
     </row>
     <row r="143">
-      <c r="D143" s="35" t="n"/>
+      <c r="A143" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="B143" s="0" t="inlineStr">
+        <is>
+          <t>Фастфуд</t>
+        </is>
+      </c>
+      <c r="C143" s="0" t="inlineStr">
+        <is>
+          <t>Супертяж</t>
+        </is>
+      </c>
+      <c r="D143" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Шаурма и кофе на набережной Корнилова</t>
+        </is>
+      </c>
       <c r="E143" s="35" t="n"/>
+      <c r="F143" s="0" t="inlineStr">
+        <is>
+          <t>набережная Корнилова, 9</t>
+        </is>
+      </c>
+      <c r="G143" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H143" s="0" t="inlineStr">
+        <is>
+          <t>44.612902, 33.518974</t>
+        </is>
+      </c>
       <c r="J143" s="36" t="n"/>
       <c r="K143" s="36" t="n"/>
       <c r="N143" s="37" t="n"/>
     </row>
     <row r="144">
-      <c r="D144" s="35" t="n"/>
+      <c r="A144" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="B144" s="0" t="inlineStr">
+        <is>
+          <t>Фастфуд</t>
+        </is>
+      </c>
+      <c r="C144" s="0" t="inlineStr">
+        <is>
+          <t>Mangal</t>
+        </is>
+      </c>
+      <c r="D144" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Шаурма и мангал на Отрадной
+✔️ Сочное мясо, свежие овощи, быстро</t>
+        </is>
+      </c>
       <c r="E144" s="35" t="n"/>
+      <c r="F144" s="0" t="inlineStr">
+        <is>
+          <t>Отрадная улица, 44</t>
+        </is>
+      </c>
+      <c r="G144" s="0" t="inlineStr">
+        <is>
+          <t>Омега</t>
+        </is>
+      </c>
+      <c r="H144" s="0" t="inlineStr">
+        <is>
+          <t>44.581588, 33.487099</t>
+        </is>
+      </c>
       <c r="J144" s="36" t="n"/>
       <c r="K144" s="36" t="n"/>
       <c r="N144" s="37" t="n"/>
     </row>
     <row r="145">
-      <c r="D145" s="35" t="n"/>
+      <c r="A145" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="B145" s="0" t="inlineStr">
+        <is>
+          <t>Шашлычные</t>
+        </is>
+      </c>
+      <c r="C145" s="0" t="inlineStr">
+        <is>
+          <t>Магазин Готового Шашлыка</t>
+        </is>
+      </c>
+      <c r="D145" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Шашлык и шаверма на вынос
+✔️ Любое мясо на выбор, завтраки</t>
+        </is>
+      </c>
       <c r="E145" s="35" t="n"/>
+      <c r="F145" s="0" t="inlineStr">
+        <is>
+          <t>площадь Восставших, 4, корп. 3</t>
+        </is>
+      </c>
+      <c r="G145" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H145" s="0" t="inlineStr">
+        <is>
+          <t>44.600968, 33.514410</t>
+        </is>
+      </c>
       <c r="J145" s="36" t="n"/>
       <c r="K145" s="36" t="n"/>
       <c r="N145" s="37" t="n"/>
     </row>
     <row r="146">
-      <c r="D146" s="35" t="n"/>
+      <c r="A146" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="B146" s="0" t="inlineStr">
+        <is>
+          <t>Пиццерии</t>
+        </is>
+      </c>
+      <c r="C146" s="0" t="inlineStr">
+        <is>
+          <t>Лола Пицца</t>
+        </is>
+      </c>
+      <c r="D146" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Пиццерия на Октябрьской Революции
+✔️ Большой выбор пицц, быстрая доставка</t>
+        </is>
+      </c>
       <c r="E146" s="35" t="n"/>
+      <c r="F146" s="0" t="inlineStr">
+        <is>
+          <t>проспект Октябрьской Революции, 24</t>
+        </is>
+      </c>
+      <c r="G146" s="0" t="inlineStr">
+        <is>
+          <t>Лётчики</t>
+        </is>
+      </c>
+      <c r="H146" s="0" t="inlineStr">
+        <is>
+          <t>44.592218, 33.455635</t>
+        </is>
+      </c>
       <c r="J146" s="36" t="n"/>
       <c r="K146" s="36" t="n"/>
       <c r="N146" s="37" t="n"/>
     </row>
     <row r="147">
-      <c r="D147" s="35" t="n"/>
+      <c r="A147" s="0" t="inlineStr">
+        <is>
+          <t>Доставки</t>
+        </is>
+      </c>
+      <c r="B147" s="0" t="inlineStr">
+        <is>
+          <t>Суши и пицца</t>
+        </is>
+      </c>
+      <c r="C147" s="0" t="inlineStr">
+        <is>
+          <t>Ёбидоёби</t>
+        </is>
+      </c>
+      <c r="D147" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Сеть доставки суши, роллов и пиццы
+✔️ Быстро и вкусно, акции</t>
+        </is>
+      </c>
       <c r="E147" s="35" t="n"/>
+      <c r="F147" s="0" t="inlineStr">
+        <is>
+          <t>Фиолентовское шоссе, 1/10</t>
+        </is>
+      </c>
+      <c r="G147" s="0" t="inlineStr">
+        <is>
+          <t>5-й км</t>
+        </is>
+      </c>
+      <c r="H147" s="0" t="inlineStr">
+        <is>
+          <t>44.547212, 33.438905</t>
+        </is>
+      </c>
       <c r="J147" s="36" t="n"/>
       <c r="K147" s="36" t="n"/>
       <c r="N147" s="37" t="n"/>
     </row>
     <row r="148">
-      <c r="D148" s="35" t="n"/>
+      <c r="A148" s="0" t="inlineStr">
+        <is>
+          <t>Доставки</t>
+        </is>
+      </c>
+      <c r="B148" s="0" t="inlineStr">
+        <is>
+          <t>Суши и пицца</t>
+        </is>
+      </c>
+      <c r="C148" s="0" t="inlineStr">
+        <is>
+          <t>Манеки Неко</t>
+        </is>
+      </c>
+      <c r="D148" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Суши и пицца с доставкой
+✔️ Бонусы и кэшбек в приложении UDS, подарки именинникам</t>
+        </is>
+      </c>
       <c r="E148" s="35" t="n"/>
+      <c r="F148" s="0" t="inlineStr">
+        <is>
+          <t>улица Гоголя, 36</t>
+        </is>
+      </c>
+      <c r="G148" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H148" s="0" t="inlineStr">
+        <is>
+          <t>44.588564, 33.516455</t>
+        </is>
+      </c>
       <c r="J148" s="36" t="n"/>
       <c r="K148" s="36" t="n"/>
       <c r="N148" s="37" t="n"/>
     </row>
     <row r="149">
-      <c r="D149" s="35" t="n"/>
+      <c r="A149" s="0" t="inlineStr">
+        <is>
+          <t>Доставки</t>
+        </is>
+      </c>
+      <c r="B149" s="0" t="inlineStr">
+        <is>
+          <t>Пицца и бургеры</t>
+        </is>
+      </c>
+      <c r="C149" s="0" t="inlineStr">
+        <is>
+          <t>Море Доставит</t>
+        </is>
+      </c>
+      <c r="D149" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Доставка пиццы и бургеров
+✔️ Пицца «Карбонара» с нежным тестом, привозят горячим</t>
+        </is>
+      </c>
       <c r="E149" s="35" t="n"/>
+      <c r="F149" s="0" t="inlineStr">
+        <is>
+          <t>Казачья улица, 60, корп. 9</t>
+        </is>
+      </c>
+      <c r="G149" s="0" t="inlineStr">
+        <is>
+          <t>Казачка</t>
+        </is>
+      </c>
+      <c r="H149" s="0" t="inlineStr">
+        <is>
+          <t>44.561578, 33.419261</t>
+        </is>
+      </c>
       <c r="J149" s="36" t="n"/>
       <c r="K149" s="36" t="n"/>
       <c r="N149" s="37" t="n"/>
     </row>
     <row r="150">
-      <c r="D150" s="35" t="n"/>
+      <c r="A150" s="0" t="inlineStr">
+        <is>
+          <t>Пекарни</t>
+        </is>
+      </c>
+      <c r="B150" s="0" t="inlineStr">
+        <is>
+          <t>Пироги на заказ</t>
+        </is>
+      </c>
+      <c r="C150" s="0" t="inlineStr">
+        <is>
+          <t>Машенькины пироги</t>
+        </is>
+      </c>
+      <c r="D150" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Пироги на песочном тесте и чизкейки по рецептам со всего мира
+✔️ Более 35 наименований, ежедневная доставка по городу</t>
+        </is>
+      </c>
       <c r="E150" s="35" t="n"/>
+      <c r="F150" s="0" t="inlineStr">
+        <is>
+          <t>Фиолентовское шоссе, 1/2</t>
+        </is>
+      </c>
+      <c r="G150" s="0" t="inlineStr">
+        <is>
+          <t>Стрелка</t>
+        </is>
+      </c>
+      <c r="H150" s="0" t="inlineStr">
+        <is>
+          <t>44.582132, 33.481296</t>
+        </is>
+      </c>
       <c r="J150" s="36" t="n"/>
       <c r="K150" s="36" t="n"/>
       <c r="N150" s="37" t="n"/>
     </row>
     <row r="151">
-      <c r="D151" s="35" t="n"/>
+      <c r="A151" s="0" t="inlineStr">
+        <is>
+          <t>Пекарни</t>
+        </is>
+      </c>
+      <c r="B151" s="0" t="inlineStr">
+        <is>
+          <t>Сеть пекарен</t>
+        </is>
+      </c>
+      <c r="C151" s="0" t="inlineStr">
+        <is>
+          <t>Царь-хлеб</t>
+        </is>
+      </c>
+      <c r="D151" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Сеть пекарен: свежий хлеб и большой ассортимент выпечки</t>
+        </is>
+      </c>
       <c r="E151" s="35" t="n"/>
+      <c r="F151" s="0" t="inlineStr">
+        <is>
+          <t>улица Супруна, 21</t>
+        </is>
+      </c>
+      <c r="G151" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H151" s="0" t="inlineStr">
+        <is>
+          <t>44.587882, 33.519057</t>
+        </is>
+      </c>
       <c r="J151" s="36" t="n"/>
       <c r="K151" s="36" t="n"/>
       <c r="N151" s="37" t="n"/>
     </row>
     <row r="152">
-      <c r="D152" s="35" t="n"/>
+      <c r="A152" s="0" t="inlineStr">
+        <is>
+          <t>Пекарни</t>
+        </is>
+      </c>
+      <c r="B152" s="0" t="inlineStr">
+        <is>
+          <t>Сеть пекарен</t>
+        </is>
+      </c>
+      <c r="C152" s="0" t="inlineStr">
+        <is>
+          <t>Царь-хлеб</t>
+        </is>
+      </c>
+      <c r="D152" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Пекарня на проспекте Победы
+✔️ Свежий хлеб с пылу с жару</t>
+        </is>
+      </c>
       <c r="E152" s="35" t="n"/>
+      <c r="F152" s="0" t="inlineStr">
+        <is>
+          <t>проспект Победы, 38В</t>
+        </is>
+      </c>
+      <c r="G152" s="0" t="inlineStr">
+        <is>
+          <t>Победа</t>
+        </is>
+      </c>
+      <c r="H152" s="0" t="inlineStr">
+        <is>
+          <t>44.587349, 33.559646</t>
+        </is>
+      </c>
       <c r="J152" s="36" t="n"/>
       <c r="K152" s="36" t="n"/>
       <c r="N152" s="37" t="n"/>
     </row>
     <row r="153">
-      <c r="D153" s="35" t="n"/>
+      <c r="A153" s="0" t="inlineStr">
+        <is>
+          <t>Пекарни</t>
+        </is>
+      </c>
+      <c r="B153" s="0" t="inlineStr">
+        <is>
+          <t>Сеть пекарен</t>
+        </is>
+      </c>
+      <c r="C153" s="0" t="inlineStr">
+        <is>
+          <t>Царь-хлеб</t>
+        </is>
+      </c>
+      <c r="D153" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Пекарня на Токарева
+✔️ Хлеб, пироговые, сладости</t>
+        </is>
+      </c>
       <c r="E153" s="35" t="n"/>
+      <c r="F153" s="0" t="inlineStr">
+        <is>
+          <t>улица Токарева, 2В</t>
+        </is>
+      </c>
+      <c r="G153" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H153" s="0" t="inlineStr">
+        <is>
+          <t>44.582280, 33.503900</t>
+        </is>
+      </c>
       <c r="J153" s="36" t="n"/>
       <c r="K153" s="36" t="n"/>
       <c r="N153" s="37" t="n"/>
     </row>
     <row r="154">
-      <c r="D154" s="35" t="n"/>
+      <c r="A154" s="0" t="inlineStr">
+        <is>
+          <t>Пекарни</t>
+        </is>
+      </c>
+      <c r="B154" s="0" t="inlineStr">
+        <is>
+          <t>Осетинские пироги</t>
+        </is>
+      </c>
+      <c r="C154" s="0" t="inlineStr">
+        <is>
+          <t>Kurtat</t>
+        </is>
+      </c>
+      <c r="D154" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Осетинские пироги с доставкой
+✔️ Сочный мясной фыдджын, горячие прямо из печи</t>
+        </is>
+      </c>
       <c r="E154" s="35" t="n"/>
+      <c r="F154" s="0" t="inlineStr">
+        <is>
+          <t>улица Тараса Шевченко, 46</t>
+        </is>
+      </c>
+      <c r="G154" s="0" t="inlineStr">
+        <is>
+          <t>Омега</t>
+        </is>
+      </c>
+      <c r="H154" s="0" t="inlineStr">
+        <is>
+          <t>44.573311, 33.457525</t>
+        </is>
+      </c>
       <c r="J154" s="36" t="n"/>
       <c r="K154" s="36" t="n"/>
       <c r="N154" s="37" t="n"/>
     </row>
     <row r="155">
-      <c r="D155" s="35" t="n"/>
+      <c r="A155" s="0" t="inlineStr">
+        <is>
+          <t>Пекарни</t>
+        </is>
+      </c>
+      <c r="C155" s="0" t="inlineStr">
+        <is>
+          <t>Из печи</t>
+        </is>
+      </c>
+      <c r="D155" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Пекарня на Северной стороне
+✔️ Свежие элеши, ассортимент меняется</t>
+        </is>
+      </c>
       <c r="E155" s="35" t="n"/>
+      <c r="F155" s="0" t="inlineStr">
+        <is>
+          <t>улица Челюскинцев, 57/3</t>
+        </is>
+      </c>
+      <c r="G155" s="0" t="inlineStr">
+        <is>
+          <t>Северная</t>
+        </is>
+      </c>
+      <c r="H155" s="0" t="inlineStr">
+        <is>
+          <t>44.639028, 33.539508</t>
+        </is>
+      </c>
       <c r="J155" s="36" t="n"/>
       <c r="K155" s="36" t="n"/>
       <c r="N155" s="37" t="n"/>
     </row>
     <row r="156">
-      <c r="D156" s="35" t="n"/>
+      <c r="A156" s="0" t="inlineStr">
+        <is>
+          <t>Кофе</t>
+        </is>
+      </c>
+      <c r="C156" s="0" t="inlineStr">
+        <is>
+          <t>Добро Кофе</t>
+        </is>
+      </c>
+      <c r="D156" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Кофейня на площади Захарова (Северная)
+✔️ Вкусный кофе и свежие булочки, необычный интерьер</t>
+        </is>
+      </c>
       <c r="E156" s="35" t="n"/>
+      <c r="F156" s="0" t="inlineStr">
+        <is>
+          <t>площадь Генерала Захарова, 5</t>
+        </is>
+      </c>
+      <c r="G156" s="0" t="inlineStr">
+        <is>
+          <t>Северная</t>
+        </is>
+      </c>
+      <c r="H156" s="0" t="inlineStr">
+        <is>
+          <t>44.627436, 33.536556</t>
+        </is>
+      </c>
       <c r="J156" s="36" t="n"/>
       <c r="K156" s="36" t="n"/>
       <c r="N156" s="37" t="n"/>
     </row>
     <row r="157">
-      <c r="D157" s="35" t="n"/>
+      <c r="A157" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C157" s="0" t="inlineStr">
+        <is>
+          <t>Похлёбкин</t>
+        </is>
+      </c>
+      <c r="D157" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Кафе домашней кухни на Руднева</t>
+        </is>
+      </c>
       <c r="E157" s="35" t="n"/>
+      <c r="F157" s="0" t="inlineStr">
+        <is>
+          <t>улица Руднева, 35А</t>
+        </is>
+      </c>
+      <c r="G157" s="0" t="inlineStr">
+        <is>
+          <t>Стрелка</t>
+        </is>
+      </c>
+      <c r="H157" s="0" t="inlineStr">
+        <is>
+          <t>44.590724, 33.492983</t>
+        </is>
+      </c>
       <c r="J157" s="36" t="n"/>
       <c r="K157" s="36" t="n"/>
       <c r="N157" s="37" t="n"/>
     </row>
     <row r="158">
-      <c r="D158" s="35" t="n"/>
+      <c r="A158" s="0" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C158" s="0" t="inlineStr">
+        <is>
+          <t>Пьеро</t>
+        </is>
+      </c>
+      <c r="D158" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Кафе на улице Ленина</t>
+        </is>
+      </c>
       <c r="E158" s="35" t="n"/>
+      <c r="F158" s="0" t="inlineStr">
+        <is>
+          <t>улица Ленина, 74</t>
+        </is>
+      </c>
+      <c r="G158" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H158" s="0" t="inlineStr">
+        <is>
+          <t>44.602290, 33.525145</t>
+        </is>
+      </c>
       <c r="J158" s="36" t="n"/>
       <c r="K158" s="36" t="n"/>
       <c r="N158" s="37" t="n"/>
     </row>
     <row r="159">
-      <c r="D159" s="35" t="n"/>
+      <c r="A159" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="B159" s="0" t="inlineStr">
+        <is>
+          <t>Восточная кухня</t>
+        </is>
+      </c>
+      <c r="C159" s="0" t="inlineStr">
+        <is>
+          <t>Арарат</t>
+        </is>
+      </c>
+      <c r="D159" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Ресторан восточной кухни на Вакуленчука
+✔️ Шашлык, люля, хачапури</t>
+        </is>
+      </c>
       <c r="E159" s="35" t="n"/>
+      <c r="F159" s="0" t="inlineStr">
+        <is>
+          <t>улица Вакуленчука, 41</t>
+        </is>
+      </c>
+      <c r="G159" s="0" t="inlineStr">
+        <is>
+          <t>Стрелка</t>
+        </is>
+      </c>
+      <c r="H159" s="0" t="inlineStr">
+        <is>
+          <t>44.586491, 33.479721</t>
+        </is>
+      </c>
       <c r="J159" s="36" t="n"/>
       <c r="K159" s="36" t="n"/>
       <c r="N159" s="37" t="n"/>
     </row>
     <row r="160">
-      <c r="D160" s="35" t="n"/>
+      <c r="A160" s="0" t="inlineStr">
+        <is>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="C160" s="0" t="inlineStr">
+        <is>
+          <t>Балалайка</t>
+        </is>
+      </c>
+      <c r="D160" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Ресторан на Большой Морской
+✔️ Русская кухня, банкеты</t>
+        </is>
+      </c>
       <c r="E160" s="35" t="n"/>
+      <c r="F160" s="0" t="inlineStr">
+        <is>
+          <t>Большая Морская, 52/2</t>
+        </is>
+      </c>
+      <c r="G160" s="0" t="inlineStr">
+        <is>
+          <t>Центр</t>
+        </is>
+      </c>
+      <c r="H160" s="0" t="inlineStr">
+        <is>
+          <t>44.602031, 33.523361</t>
+        </is>
+      </c>
       <c r="J160" s="36" t="n"/>
       <c r="K160" s="36" t="n"/>
       <c r="N160" s="37" t="n"/>
@@ -13358,7 +14372,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="25.25" customWidth="1" style="38" min="2" max="2"/>
@@ -14186,6 +15200,681 @@
       <c r="E31" s="0" t="inlineStr">
         <is>
           <t>44.495616, 33.592308</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Достопримечательности</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Графская пристань</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Парадная пристань Севастополя с белоснежной колоннадой 1846 года. Отсюда отправляются катера и морские прогулки по бухте.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>площадь Нахимова</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>44.616988, 33.526723</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Достопримечательности</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Памятник затопленным кораблям</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Символ Севастополя: колонна с бронзовым орлом стоит прямо в море у Приморского бульвара. Память о кораблях, затопленных в 1854–1855 годах.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Приморский бульвар</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>44.618344, 33.524292</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Достопримечательности</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Площадь Нахимова</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Центральная площадь города с мемориалом героической обороны Севастополя 1941–1942 годов.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>центр</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>44.616658, 33.523904</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Достопримечательности</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Исторический бульвар</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Зелёный бульвар на месте 4-го бастиона: аллеи, памятники, панорама «Оборона Севастополя».</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>4-я Бастионная</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>44.596660, 33.523915</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Достопримечательности</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Башня Ветров</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Памятник архитектуры 1849 года на улице Фрунзе — башня-вентиляция старой Морской библиотеки.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Фрунзе, 5</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>44.611004, 33.524059</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Достопримечательности</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Владимирский собор</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Собор-усыпальница адмиралов: здесь покоятся Лазарев, Корнилов, Нахимов, Истомин.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Суворова, 3</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>44.610493, 33.523600</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Достопримечательности</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Памятник Солдату и Матросу</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>40-метровый монумент героям освобождения Севастополя 1944 года на мысе Хрустальном.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>мыс Хрустальный, Капитанская</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>44.615155, 33.514324</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Достопримечательности</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Мыс Хрустальный</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Мыс в центре города между Артиллерийской и Карантинной бухтами. Рядом пляж и монумент Солдату и Матросу.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Капитанская улица</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>44.615500, 33.531500</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Достопримечательности</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Мыс Айя</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Заповедный мыс с реликтовыми соснами Станкевича, гротами и дикими пляжами у Ласпи.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Балаклава, заказник</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>44.428371, 33.654537</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Достопримечательности</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Херсонесский маяк</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Знаменитый маяк 1816 года на самой западной точке Крыма. Сам маяк на закрытой территории — вид со смотровой площадки.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>мыс Херсонес</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>44.583227, 33.380907</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Достопримечательности</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Крепость Чембало</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Генуэзская крепость XIV–XV веков на горе над Балаклавой. Сохранились башни и стены, с вершины — лучший вид на бухту.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Балаклава, набережная Назукина</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>44.494750, 33.599502</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Достопримечательности</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Крепость Каламита</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Средневековая крепость на Монастырской скале над Инкерманом. Сохранились башни и остатки стен.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Инкерман</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>44.602700, 33.608900</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Достопримечательности</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Балаклавская бухта</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Узкая живописная бухта, набережная Назукина с яхтами и кафе, вид на Чембало.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Балаклава</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>44.495234, 33.594140</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Достопримечательности</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Свято-Георгиевский монастырь</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Древний монастырь на краю обрыва над морем. Смотровая площадка, отсюда спуск к Яшмовому пляжу.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Фиолент</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>44.505438, 33.509964</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Достопримечательности</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Свято-Климентовский пещерный монастырь</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Пещерный монастырь, вырубленный в скалах в VIII–IX веках. Действующий, вход свободный.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Инкерман, Симферопольское шоссе</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>44.604080, 33.607756</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Музеи</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Панорама «Оборона Севастополя 1854–1855»</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Грандиозное живописное полотно обороны города — одно из крупнейших в мире, с предметным планом.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Исторический бульвар</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>44.595501, 33.523309</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Музеи</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Малахов курган</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Мемориальный комплекс с Оборонительной башней Корниловского бастиона. Место гибели адмиралов Корнилова и Нахимова.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Корабельная сторона</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>44.604508, 33.548097</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Музеи</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>35-я береговая батарея</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Музейный комплекс на месте героической обороны Севастополя 1942 года: казематы, пантеон памяти, экскурсии.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Казачья бухта</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>44.558189, 33.406413</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Музеи</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Балаклавский подземный музейный комплекс</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Бывшая секретная база подводных лодок в толще горы Таврос: подземный канал и музей холодной войны.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Таврическая набережная, 22</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>44.501043, 33.596484</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Музеи</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Михайловская батарея</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Форт середины XIX века на Северной стороне с музеем Военно-морского флота и выставкой раритетов.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Громова, 35/1, Северная</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>44.628061, 33.525740</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Музеи</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Константиновская батарея</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Каменный форт 1840 года у входа в Севастопольскую бухту. Музей, вид на рейд и город с моря.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Северная, у рейда</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>44.626945, 33.512430</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Музеи</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Музей Черноморского флота</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Военно-исторический музей истории ЧФ: модели кораблей, оружие, документы, личные вещи адмиралов.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Ленина, 11</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>44.613355, 33.525772</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Музеи</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Севастопольский морской аквариум-музей</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Один из старейших аквариумов Европы (1897 год): обитатели Чёрного моря и тропиков.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>проспект Нахимова, 2</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>44.616900, 33.522400</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Музеи</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Дельфинарий в Артбухте</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Представления с дельфинами и морскими котиками в Артиллерийской бухте. Возможность поплавать с дельфинами.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>набережная Корнилова, 2</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>44.612200, 33.526400</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Музеи</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Античный театр Херсонеса</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Античный театр III века до н.э. в центре городища Херсонеса Таврического. В сезон — спектакли под открытым небом.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Херсонес</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>44.611000, 33.492000</t>
         </is>
       </c>
     </row>
@@ -15831,7 +17520,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="47.38" customWidth="1" style="38" min="3" max="3"/>
@@ -15883,6 +17572,26 @@
           <t>Пешие</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Большая Севастопольская тропа</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>117 км (этап Балаклава–Ласпи ≈14 км)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Средняя</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Маркированный маршрут вокруг города: Балаклава → Фиолент → Ласпи → Байдары → Черноречье. Самый популярный этап Балаклава–Ласпи занимает 5–6 часов.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -15890,6 +17599,26 @@
           <t>Авто</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Автокольцо: Севастополь — Ласпи — Байдарские ворота — Форос</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>≈80 км</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Лёгкая</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Смотровые площадки Ласпи и Байдарских ворот, серпантины Южного берега, спуск к морю в Ласпи.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -15897,11 +17626,132 @@
           <t>Велосипед</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Велопроменад: Парк Победы — Омега — Камышовая</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8–10 км</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Лёгкая</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ровный городской маршрут по набережной и проспекту Гагарина вдоль бухт, велодорожки в парке Победы.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Вода</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Катер Артбухта — Учкуевка</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>15–20 минут</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Лёгкая</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Морская прогулка через Севастопольскую бухту на песчаный пляж Учкуевки, виды на город с воды.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Пешие</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>800 ступеней к Яшмовому пляжу</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1,5–2 часа</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Средняя</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Спуск от Георгиевского монастыря по лестнице к Яшмовому пляжу и Скале Святого Явления. Обратно — подъём в гору.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Авто</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Фиолент — Балаклава</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>≈30 км</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Лёгкая</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Побережье: мыс Фиолент, Георгиевский монастырь, Серебряный и Золотой пляжи, набережная Балаклавы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Вода</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Морская прогулка по бухтам Севастополя</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>45–60 минут</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Лёгкая</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Экскурсия на катере от Графской пристани: рейд, бухты, вид на батареи и корабли с воды.</t>
         </is>
       </c>
     </row>

--- a/Sevastopol AI База.xlsx
+++ b/Sevastopol AI База.xlsx
@@ -8279,22 +8279,117 @@
       <c r="N160" s="37" t="n"/>
     </row>
     <row r="161">
-      <c r="D161" s="35" t="n"/>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Бары и пабы</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Пинта</t>
+        </is>
+      </c>
+      <c r="D161" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Пивной бар на проспекте Гагарина
+✔️ Разливное пиво, закуски</t>
+        </is>
+      </c>
       <c r="E161" s="35" t="n"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>проспект Гагарина, 44</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Стрелка</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>44.601834, 33.479116</t>
+        </is>
+      </c>
       <c r="J161" s="36" t="n"/>
       <c r="K161" s="36" t="n"/>
       <c r="N161" s="37" t="n"/>
     </row>
     <row r="162">
-      <c r="D162" s="35" t="n"/>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Пекарни</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Хлебный</t>
+        </is>
+      </c>
+      <c r="D162" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Пекарня на проспекте Гагарина
+✔️ Свежая выпечка и хлеб</t>
+        </is>
+      </c>
       <c r="E162" s="35" t="n"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>проспект Гагарина, 11</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Стрелка</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>44.599669, 33.487230</t>
+        </is>
+      </c>
       <c r="J162" s="36" t="n"/>
       <c r="K162" s="36" t="n"/>
       <c r="N162" s="37" t="n"/>
     </row>
     <row r="163">
-      <c r="D163" s="35" t="n"/>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Али-Баба</t>
+        </is>
+      </c>
+      <c r="D163" s="35" t="inlineStr">
+        <is>
+          <t>✔️ Кафе в ТЦ «Стрелецкий»
+✔️ Восточная кухня, быстро и сытно</t>
+        </is>
+      </c>
       <c r="E163" s="35" t="n"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>проспект Гагарина, 8 (ТЦ «Стрелецкий»)</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Стрелка</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>44.599691, 33.489818</t>
+        </is>
+      </c>
       <c r="J163" s="36" t="n"/>
       <c r="K163" s="36" t="n"/>
       <c r="N163" s="37" t="n"/>
@@ -15204,675 +15299,675 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>Достопримечательности</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>Графская пристань</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>Парадная пристань Севастополя с белоснежной колоннадой 1846 года. Отсюда отправляются катера и морские прогулки по бухте.</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>площадь Нахимова</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="0" t="inlineStr">
         <is>
           <t>44.616988, 33.526723</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>Достопримечательности</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>Памятник затопленным кораблям</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>Символ Севастополя: колонна с бронзовым орлом стоит прямо в море у Приморского бульвара. Память о кораблях, затопленных в 1854–1855 годах.</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>Приморский бульвар</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t>44.618344, 33.524292</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>Достопримечательности</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>Площадь Нахимова</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>Центральная площадь города с мемориалом героической обороны Севастополя 1941–1942 годов.</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
         <is>
           <t>центр</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="0" t="inlineStr">
         <is>
           <t>44.616658, 33.523904</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>Достопримечательности</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>Исторический бульвар</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>Зелёный бульвар на месте 4-го бастиона: аллеи, памятники, панорама «Оборона Севастополя».</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="0" t="inlineStr">
         <is>
           <t>4-я Бастионная</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="0" t="inlineStr">
         <is>
           <t>44.596660, 33.523915</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>Достопримечательности</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>Башня Ветров</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>Памятник архитектуры 1849 года на улице Фрунзе — башня-вентиляция старой Морской библиотеки.</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="0" t="inlineStr">
         <is>
           <t>Фрунзе, 5</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="0" t="inlineStr">
         <is>
           <t>44.611004, 33.524059</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
         <is>
           <t>Достопримечательности</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>Владимирский собор</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>Собор-усыпальница адмиралов: здесь покоятся Лазарев, Корнилов, Нахимов, Истомин.</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="0" t="inlineStr">
         <is>
           <t>Суворова, 3</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="0" t="inlineStr">
         <is>
           <t>44.610493, 33.523600</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>Достопримечательности</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>Памятник Солдату и Матросу</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>40-метровый монумент героям освобождения Севастополя 1944 года на мысе Хрустальном.</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="0" t="inlineStr">
         <is>
           <t>мыс Хрустальный, Капитанская</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="0" t="inlineStr">
         <is>
           <t>44.615155, 33.514324</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>Достопримечательности</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>Мыс Хрустальный</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>Мыс в центре города между Артиллерийской и Карантинной бухтами. Рядом пляж и монумент Солдату и Матросу.</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="0" t="inlineStr">
         <is>
           <t>Капитанская улица</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="0" t="inlineStr">
         <is>
           <t>44.615500, 33.531500</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
         <is>
           <t>Достопримечательности</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>Мыс Айя</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>Заповедный мыс с реликтовыми соснами Станкевича, гротами и дикими пляжами у Ласпи.</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="0" t="inlineStr">
         <is>
           <t>Балаклава, заказник</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="0" t="inlineStr">
         <is>
           <t>44.428371, 33.654537</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>Достопримечательности</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>Херсонесский маяк</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>Знаменитый маяк 1816 года на самой западной точке Крыма. Сам маяк на закрытой территории — вид со смотровой площадки.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
         <is>
           <t>мыс Херсонес</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="0" t="inlineStr">
         <is>
           <t>44.583227, 33.380907</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="0" t="inlineStr">
         <is>
           <t>Достопримечательности</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>Крепость Чембало</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>Генуэзская крепость XIV–XV веков на горе над Балаклавой. Сохранились башни и стены, с вершины — лучший вид на бухту.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
         <is>
           <t>Балаклава, набережная Назукина</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t>44.494750, 33.599502</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="0" t="inlineStr">
         <is>
           <t>Достопримечательности</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>Крепость Каламита</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>Средневековая крепость на Монастырской скале над Инкерманом. Сохранились башни и остатки стен.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
         <is>
           <t>Инкерман</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="0" t="inlineStr">
         <is>
           <t>44.602700, 33.608900</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="0" t="inlineStr">
         <is>
           <t>Достопримечательности</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>Балаклавская бухта</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
         <is>
           <t>Узкая живописная бухта, набережная Назукина с яхтами и кафе, вид на Чембало.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="0" t="inlineStr">
         <is>
           <t>Балаклава</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="0" t="inlineStr">
         <is>
           <t>44.495234, 33.594140</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="0" t="inlineStr">
         <is>
           <t>Достопримечательности</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>Свято-Георгиевский монастырь</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t>Древний монастырь на краю обрыва над морем. Смотровая площадка, отсюда спуск к Яшмовому пляжу.</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
         <is>
           <t>Фиолент</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="0" t="inlineStr">
         <is>
           <t>44.505438, 33.509964</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="0" t="inlineStr">
         <is>
           <t>Достопримечательности</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>Свято-Климентовский пещерный монастырь</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>Пещерный монастырь, вырубленный в скалах в VIII–IX веках. Действующий, вход свободный.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
         <is>
           <t>Инкерман, Симферопольское шоссе</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="0" t="inlineStr">
         <is>
           <t>44.604080, 33.607756</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="0" t="inlineStr">
         <is>
           <t>Музеи</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>Панорама «Оборона Севастополя 1854–1855»</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>Грандиозное живописное полотно обороны города — одно из крупнейших в мире, с предметным планом.</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>Исторический бульвар</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="0" t="inlineStr">
         <is>
           <t>44.595501, 33.523309</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="0" t="inlineStr">
         <is>
           <t>Музеи</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>Малахов курган</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>Мемориальный комплекс с Оборонительной башней Корниловского бастиона. Место гибели адмиралов Корнилова и Нахимова.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="0" t="inlineStr">
         <is>
           <t>Корабельная сторона</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="0" t="inlineStr">
         <is>
           <t>44.604508, 33.548097</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="0" t="inlineStr">
         <is>
           <t>Музеи</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>35-я береговая батарея</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>Музейный комплекс на месте героической обороны Севастополя 1942 года: казематы, пантеон памяти, экскурсии.</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
         <is>
           <t>Казачья бухта</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="0" t="inlineStr">
         <is>
           <t>44.558189, 33.406413</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="0" t="inlineStr">
         <is>
           <t>Музеи</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>Балаклавский подземный музейный комплекс</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>Бывшая секретная база подводных лодок в толще горы Таврос: подземный канал и музей холодной войны.</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
         <is>
           <t>Таврическая набережная, 22</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="0" t="inlineStr">
         <is>
           <t>44.501043, 33.596484</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="0" t="inlineStr">
         <is>
           <t>Музеи</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>Михайловская батарея</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>Форт середины XIX века на Северной стороне с музеем Военно-морского флота и выставкой раритетов.</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="0" t="inlineStr">
         <is>
           <t>Громова, 35/1, Северная</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="0" t="inlineStr">
         <is>
           <t>44.628061, 33.525740</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="0" t="inlineStr">
         <is>
           <t>Музеи</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>Константиновская батарея</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr">
         <is>
           <t>Каменный форт 1840 года у входа в Севастопольскую бухту. Музей, вид на рейд и город с моря.</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="0" t="inlineStr">
         <is>
           <t>Северная, у рейда</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="0" t="inlineStr">
         <is>
           <t>44.626945, 33.512430</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="0" t="inlineStr">
         <is>
           <t>Музеи</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>Музей Черноморского флота</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>Военно-исторический музей истории ЧФ: модели кораблей, оружие, документы, личные вещи адмиралов.</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="0" t="inlineStr">
         <is>
           <t>Ленина, 11</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="0" t="inlineStr">
         <is>
           <t>44.613355, 33.525772</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="0" t="inlineStr">
         <is>
           <t>Музеи</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>Севастопольский морской аквариум-музей</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>Один из старейших аквариумов Европы (1897 год): обитатели Чёрного моря и тропиков.</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="0" t="inlineStr">
         <is>
           <t>проспект Нахимова, 2</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="0" t="inlineStr">
         <is>
           <t>44.616900, 33.522400</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="0" t="inlineStr">
         <is>
           <t>Музеи</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>Дельфинарий в Артбухте</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
         <is>
           <t>Представления с дельфинами и морскими котиками в Артиллерийской бухте. Возможность поплавать с дельфинами.</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="0" t="inlineStr">
         <is>
           <t>набережная Корнилова, 2</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="0" t="inlineStr">
         <is>
           <t>44.612200, 33.526400</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="0" t="inlineStr">
         <is>
           <t>Музеи</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>Античный театр Херсонеса</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr">
         <is>
           <t>Античный театр III века до н.э. в центре городища Херсонеса Таврического. В сезон — спектакли под открытым небом.</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="0" t="inlineStr">
         <is>
           <t>Херсонес</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="0" t="inlineStr">
         <is>
           <t>44.611000, 33.492000</t>
         </is>
@@ -17572,22 +17667,22 @@
           <t>Пешие</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>Большая Севастопольская тропа</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>117 км (этап Балаклава–Ласпи ≈14 км)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>Средняя</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>Маркированный маршрут вокруг города: Балаклава → Фиолент → Ласпи → Байдары → Черноречье. Самый популярный этап Балаклава–Ласпи занимает 5–6 часов.</t>
         </is>
@@ -17599,22 +17694,22 @@
           <t>Авто</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Автокольцо: Севастополь — Ласпи — Байдарские ворота — Форос</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>≈80 км</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>Лёгкая</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>Смотровые площадки Ласпи и Байдарских ворот, серпантины Южного берега, спуск к морю в Ласпи.</t>
         </is>
@@ -17626,22 +17721,22 @@
           <t>Велосипед</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>Велопроменад: Парк Победы — Омега — Камышовая</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>8–10 км</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>Лёгкая</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Ровный городской маршрут по набережной и проспекту Гагарина вдоль бухт, велодорожки в парке Победы.</t>
         </is>
@@ -17653,103 +17748,103 @@
           <t>Вода</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Катер Артбухта — Учкуевка</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>15–20 минут</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>Лёгкая</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>Морская прогулка через Севастопольскую бухту на песчаный пляж Учкуевки, виды на город с воды.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>Пешие</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>800 ступеней к Яшмовому пляжу</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>1,5–2 часа</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>Средняя</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>Спуск от Георгиевского монастыря по лестнице к Яшмовому пляжу и Скале Святого Явления. Обратно — подъём в гору.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>Авто</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>Фиолент — Балаклава</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>≈30 км</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>Лёгкая</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>Побережье: мыс Фиолент, Георгиевский монастырь, Серебряный и Золотой пляжи, набережная Балаклавы.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>Вода</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>Морская прогулка по бухтам Севастополя</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>45–60 минут</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>Лёгкая</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>Экскурсия на катере от Графской пристани: рейд, бухты, вид на батареи и корабли с воды.</t>
         </is>

--- a/Sevastopol AI База.xlsx
+++ b/Sevastopol AI База.xlsx
@@ -8279,17 +8279,17 @@
       <c r="N160" s="37" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="A161" s="0" t="inlineStr">
         <is>
           <t>Кафе</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B161" s="0" t="inlineStr">
         <is>
           <t>Бары и пабы</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="C161" s="0" t="inlineStr">
         <is>
           <t>Пинта</t>
         </is>
@@ -8301,17 +8301,17 @@
         </is>
       </c>
       <c r="E161" s="35" t="n"/>
-      <c r="F161" t="inlineStr">
+      <c r="F161" s="0" t="inlineStr">
         <is>
           <t>проспект Гагарина, 44</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="G161" s="0" t="inlineStr">
         <is>
           <t>Стрелка</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
+      <c r="H161" s="0" t="inlineStr">
         <is>
           <t>44.601834, 33.479116</t>
         </is>
@@ -8321,12 +8321,12 @@
       <c r="N161" s="37" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
+      <c r="A162" s="0" t="inlineStr">
         <is>
           <t>Пекарни</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
+      <c r="C162" s="0" t="inlineStr">
         <is>
           <t>Хлебный</t>
         </is>
@@ -8338,17 +8338,17 @@
         </is>
       </c>
       <c r="E162" s="35" t="n"/>
-      <c r="F162" t="inlineStr">
+      <c r="F162" s="0" t="inlineStr">
         <is>
           <t>проспект Гагарина, 11</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
+      <c r="G162" s="0" t="inlineStr">
         <is>
           <t>Стрелка</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
+      <c r="H162" s="0" t="inlineStr">
         <is>
           <t>44.599669, 33.487230</t>
         </is>
@@ -8358,12 +8358,12 @@
       <c r="N162" s="37" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
+      <c r="A163" s="0" t="inlineStr">
         <is>
           <t>Кафе</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C163" s="0" t="inlineStr">
         <is>
           <t>Али-Баба</t>
         </is>
@@ -8375,17 +8375,17 @@
         </is>
       </c>
       <c r="E163" s="35" t="n"/>
-      <c r="F163" t="inlineStr">
+      <c r="F163" s="0" t="inlineStr">
         <is>
           <t>проспект Гагарина, 8 (ТЦ «Стрелецкий»)</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="G163" s="0" t="inlineStr">
         <is>
           <t>Стрелка</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="H163" s="0" t="inlineStr">
         <is>
           <t>44.599691, 33.489818</t>
         </is>
@@ -14768,6 +14768,11 @@
           <t>Памятник затопленным кораблям</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>44.617031, 33.523836</t>
+        </is>
+      </c>
       <c r="F11" s="4" t="n"/>
     </row>
     <row r="12">
@@ -14789,6 +14794,11 @@
       <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Новый Херсонес</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>44.610846, 33.490369</t>
         </is>
       </c>
       <c r="F12" s="4" t="n"/>
@@ -14881,6 +14891,11 @@
           <t>Бухта Ласпи</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>44.430924, 33.714012</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -14903,6 +14918,11 @@
           <t>Байдарский перевал</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>44.406184, 33.782023</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -14925,6 +14945,11 @@
           <t>Мемориальный комплекс "Сапун-гора"</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>44.555924, 33.585154</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -14947,6 +14972,11 @@
           <t>Фиолент, Царское Село</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>44.509850, 33.478403</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -14969,6 +14999,11 @@
           <t>Балаклава</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>44.516074, 33.568122</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -14991,6 +15026,11 @@
           <t>Балаклава</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>44.463600, 33.642700</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -15011,6 +15051,11 @@
       <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Яшмовый пляж</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>44.502900, 33.505800</t>
         </is>
       </c>
     </row>
@@ -15996,7 +16041,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="44.63" customWidth="1" style="38" min="4" max="4"/>
@@ -16087,6 +16132,665 @@
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Вечеринки</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>Концерты</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Севастопольский центр культуры и искусств</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Концерт «Музыкальный калейдоскоп»</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>✔️ От 700 ₽, 6+
+✔️ Действует Пушкинская карта</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>https://afisha.sevastopol.press/event/7367537</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>Концерты</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>19.09.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Дом офицеров флота (Ленина, 9)</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Театрально-музыкально-поэтический диалог «Ритм и рифма»</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>✔️ Вход свободный</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>https://afisha.sevastopol.press/event/-891</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>Концерты</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>20.09.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Дом офицеров флота (Ленина, 9)</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Гала-концерт фестиваля фламенко «Sobre las Olas»</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>✔️ Вход свободный
+✔️ Испанское фламенко на сцене ДОФ</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>https://afisha.sevastopol.press/event/-890</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>Концерты</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>20.09.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Экопространство «Али-Баир», Байдарская долина</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>«Кино на струнах» с дуэтом виолончелей</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>✔️ 1200 ₽
+✔️ Саундтреки из кино в горах Байдарской долины</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>https://afisha.sevastopol.press/event/-888</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>Концерты</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Севастопольский центр культуры и искусств</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Трансляция концерта Госоркестра им. Светланова</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>✔️ Вход свободный
+✔️ Трансляция на большом экране</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>https://afisha.sevastopol.press/event/7330711</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>Концерты</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>11.10.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Скельская пещера</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>«Инструментальное путешествие» в Скельской пещере</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>✔️ 1500 ₽, 6+
+✔️ Концерт в пещере с уникальной акустикой</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>https://afisha.sevastopol.press/event/-889</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>Концерты</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>31.10.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Кинотеатр «Украина»</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Концерт «Сопрано в опере»</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>✔️ От 600 ₽, 6+
+✔️ Хиты мировой оперы</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>https://afisha.sevastopol.press/event/7408583</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>Концерты</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>08.11.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Дворец культуры рыбаков</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Концерт группы «Ундервуд»</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>✔️ От 1500 ₽, 18+
+✔️ «Гагарин, я вас любила» и другие хиты</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>https://afisha.sevastopol.press/event/-656</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>Театр</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Театр им. Луначарского (пр. Нахимова, 6)</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Спектакль «Ревизор»</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>✔️ Гоголь, комедия 12+
+✔️ Начало в 18:00</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>Театр</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Театр им. Луначарского (пр. Нахимова, 6)</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Оперетта «Севастопольский вальс»</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>✔️ Героико-романтическая музыкальная история 12+
+✔️ Начало в 18:00</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>Театр</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>19.09.2026</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Театр им. Луначарского (пр. Нахимова, 6)</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Экскурсия по театру</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>✔️ Закулисье главного театра города, 6+
+✔️ Начало в 13:00</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>Театр</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>19.09.2026</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Театр им. Луначарского (пр. Нахимова, 6)</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Спектакль «Мастер и Маргарита»</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>✔️ Булгаков, 18+
+✔️ Начало в 17:00</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>Театр</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>20.09.2026</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Театр им. Луначарского (пр. Нахимова, 6)</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Премьера «Преступление и наказание»</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>✔️ Достоевский, драма 16+
+✔️ Начало в 17:00</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>Театр</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Дом офицеров флота (Ленина, 9)</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Комедия «Любовь на бис»</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>✔️ От 2500 ₽
+✔️ Начало в 19:00</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>https://www.afisha.ru/sevastopol/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>Театр</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>22.09.2026</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>Театр им. Луначарского (пр. Нахимова, 6)</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>Спектакль «Обыкновенное чудо»</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>✔️ Посвящение Учителю в 2-х частях, 12+
+✔️ Начало в 18:00</t>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>Театр</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>Театр им. Луначарского (пр. Нахимова, 6)</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>Спектакль «Горе от ума»</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>✔️ Грибоедов, комедия 12+
+✔️ Начало в 18:00</t>
+        </is>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>Театр</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>Театр им. Луначарского (пр. Нахимова, 6)</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>Спектакль «Бесы»</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>✔️ Достоевский, 16+
+✔️ Начало в 18:00</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>Театр</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>27.09.2026</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>Театр им. Луначарского (пр. Нахимова, 6)</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>Спектакль «Доктор Живаго»</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>✔️ Пастернак, драма 16+
+✔️ Начало в 17:00</t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>Театр</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>03.10.2026</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>Театр им. Луначарского (пр. Нахимова, 6)</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>Спектакль «Три сестры»</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>✔️ Чехов, 16+
+✔️ Начало в 18:00</t>
+        </is>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>Выставки</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>Музей обороны Севастополя</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>Выставка «РУБО. 170 лет...»</t>
+        </is>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>✔️ К 170-летию Франца Рубо и окончания Крымской войны
+✔️ Работает до 25 октября</t>
+        </is>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>https://sevmuseum.ru/events/</t>
         </is>
       </c>
     </row>

--- a/Sevastopol AI База.xlsx
+++ b/Sevastopol AI База.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P984"/>
+  <dimension ref="A1:P983"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="17" customWidth="1" style="45" min="1" max="1"/>
@@ -9351,61 +9351,57 @@
       </c>
       <c r="C131" s="34" t="inlineStr">
         <is>
-          <t>Супертяж</t>
+          <t>Mangal</t>
         </is>
       </c>
       <c r="D131" s="37" t="inlineStr">
         <is>
-          <t>✔️ Шаурма и кофе на 
-площади 300-летия Российского Флота</t>
+          <t>✔️ Шаурма и мангал на Отрадной
+✔️ Сочное мясо, свежие овощи, быстро</t>
         </is>
       </c>
       <c r="E131" s="37" t="n"/>
       <c r="F131" s="34" t="inlineStr">
         <is>
+          <t>Отрадная улица, 44</t>
+        </is>
+      </c>
+      <c r="G131" s="34" t="inlineStr">
+        <is>
+          <t>Омега</t>
+        </is>
+      </c>
+      <c r="H131" s="34" t="inlineStr">
+        <is>
+          <t>44.581588, 33.487099</t>
+        </is>
+      </c>
+      <c r="I131" s="32" t="inlineStr">
+        <is>
+          <t>https://avatars.mds.yandex.net/get-altay/4441482/2a000001782bee2efa68ae8291adbd8add2a/XXXL</t>
+        </is>
+      </c>
+      <c r="J131" s="30" t="inlineStr">
+        <is>
+          <t>https://vk.ru/mangal__92</t>
+        </is>
+      </c>
+      <c r="K131" s="41" t="n"/>
+      <c r="L131" s="35" t="n"/>
+      <c r="M131" s="29" t="inlineStr">
+        <is>
+          <t>https://mangal92.ru</t>
+        </is>
+      </c>
+      <c r="N131" s="44" t="inlineStr">
+        <is>
           <t xml:space="preserve">
-площадь 300-летия Российского Флота, 2</t>
-        </is>
-      </c>
-      <c r="G131" s="34" t="inlineStr">
-        <is>
-          <t>Центр</t>
-        </is>
-      </c>
-      <c r="H131" s="34" t="inlineStr">
-        <is>
-          <t>44.613171, 33.518784</t>
-        </is>
-      </c>
-      <c r="I131" s="32" t="inlineStr">
-        <is>
-          <t>https://avatars.mds.yandex.net/get-altay/19091395/2a0000019ef033aa6b9f32265f832cd74dc0/XXXL</t>
-        </is>
-      </c>
-      <c r="J131" s="39" t="inlineStr">
-        <is>
-          <t>https://vk.ru/supertyazh</t>
-        </is>
-      </c>
-      <c r="K131" s="30" t="inlineStr">
-        <is>
-          <t>https://t.me/supertyazhsev</t>
-        </is>
-      </c>
-      <c r="L131" s="35" t="n"/>
-      <c r="M131" s="32" t="inlineStr">
-        <is>
-          <t>https://xn--80aalcfyojggmjqk8p.xn--p1ai/</t>
-        </is>
-      </c>
-      <c r="N131" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> +7 (978) 777-66-09</t>
++7 (978) 212-50-99</t>
         </is>
       </c>
       <c r="O131" s="35" t="inlineStr">
         <is>
-          <t>ежедневно 10:00-01:00</t>
+          <t>ежедневно 10:00-20:00</t>
         </is>
       </c>
       <c r="P131" s="35" t="inlineStr">
@@ -9422,62 +9418,65 @@
       </c>
       <c r="B132" s="34" t="inlineStr">
         <is>
-          <t>Фастфуд</t>
+          <t>Шашлычные</t>
         </is>
       </c>
       <c r="C132" s="34" t="inlineStr">
         <is>
-          <t>Mangal</t>
+          <t>Магазин Готового Шашлыка</t>
         </is>
       </c>
       <c r="D132" s="37" t="inlineStr">
         <is>
-          <t>✔️ Шаурма и мангал на Отрадной
-✔️ Сочное мясо, свежие овощи, быстро</t>
+          <t>✔️ Шашлык и шаверма на вынос
+✔️ Любое мясо на выбор, завтраки</t>
         </is>
       </c>
       <c r="E132" s="37" t="n"/>
       <c r="F132" s="34" t="inlineStr">
         <is>
-          <t>Отрадная улица, 44</t>
+          <t>площадь Восставших, 4, корп. 3</t>
         </is>
       </c>
       <c r="G132" s="34" t="inlineStr">
         <is>
-          <t>Омега</t>
+          <t>Центр</t>
         </is>
       </c>
       <c r="H132" s="34" t="inlineStr">
         <is>
-          <t>44.581588, 33.487099</t>
+          <t>44.600968, 33.514410</t>
         </is>
       </c>
       <c r="I132" s="32" t="inlineStr">
         <is>
-          <t>https://avatars.mds.yandex.net/get-altay/4441482/2a000001782bee2efa68ae8291adbd8add2a/XXXL</t>
+          <t>https://avatars.mds.yandex.net/get-altay/4280929/2a000001782c8b96f90e2e5e857aa061d58a/XXXL</t>
         </is>
       </c>
       <c r="J132" s="30" t="inlineStr">
         <is>
-          <t>https://vk.ru/mangal__92</t>
-        </is>
-      </c>
-      <c r="K132" s="41" t="n"/>
+          <t>https://vk.ru/mgsh.club</t>
+        </is>
+      </c>
+      <c r="K132" s="30" t="inlineStr">
+        <is>
+          <t>https://t.me/mgshclub</t>
+        </is>
+      </c>
       <c r="L132" s="35" t="n"/>
       <c r="M132" s="29" t="inlineStr">
         <is>
-          <t>https://mangal92.ru</t>
+          <t>https://sevastopol.mgsh.ru</t>
         </is>
       </c>
       <c r="N132" s="44" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-+7 (978) 212-50-99</t>
+          <t xml:space="preserve"> +7 (978) 723-98-80</t>
         </is>
       </c>
       <c r="O132" s="35" t="inlineStr">
         <is>
-          <t>ежедневно 10:00-20:00</t>
+          <t>ежедневно 10:00-22:00</t>
         </is>
       </c>
       <c r="P132" s="35" t="inlineStr">
@@ -9494,65 +9493,66 @@
       </c>
       <c r="B133" s="34" t="inlineStr">
         <is>
-          <t>Шашлычные</t>
+          <t>Пиццерии</t>
         </is>
       </c>
       <c r="C133" s="34" t="inlineStr">
         <is>
-          <t>Магазин Готового Шашлыка</t>
+          <t>Лола Пицца</t>
         </is>
       </c>
       <c r="D133" s="37" t="inlineStr">
         <is>
-          <t>✔️ Шашлык и шаверма на вынос
-✔️ Любое мясо на выбор, завтраки</t>
+          <t>✔️ Пиццерия на Октябрьской Революции
+✔️ Большой выбор пицц, быстрая доставка</t>
         </is>
       </c>
       <c r="E133" s="37" t="n"/>
       <c r="F133" s="34" t="inlineStr">
         <is>
-          <t>площадь Восставших, 4, корп. 3</t>
+          <t>проспект Октябрьской Революции, 24</t>
         </is>
       </c>
       <c r="G133" s="34" t="inlineStr">
         <is>
-          <t>Центр</t>
+          <t>Лётчики</t>
         </is>
       </c>
       <c r="H133" s="34" t="inlineStr">
         <is>
-          <t>44.600968, 33.514410</t>
-        </is>
-      </c>
-      <c r="I133" s="32" t="inlineStr">
-        <is>
-          <t>https://avatars.mds.yandex.net/get-altay/4280929/2a000001782c8b96f90e2e5e857aa061d58a/XXXL</t>
+          <t>44.592218, 33.455635</t>
+        </is>
+      </c>
+      <c r="I133" s="38" t="inlineStr">
+        <is>
+          <t>https://avatars.mds.yandex.net/get-altay/11419181/2a00000194b2e38ed36d35839e69b9c375ae/XXXL</t>
         </is>
       </c>
       <c r="J133" s="30" t="inlineStr">
         <is>
-          <t>https://vk.ru/mgsh.club</t>
+          <t>https://vk.ru/lolapizza_sev</t>
         </is>
       </c>
       <c r="K133" s="30" t="inlineStr">
         <is>
-          <t>https://t.me/mgshclub</t>
+          <t>https://t.me/lolapizza_podslushano</t>
         </is>
       </c>
       <c r="L133" s="35" t="n"/>
       <c r="M133" s="29" t="inlineStr">
         <is>
-          <t>https://sevastopol.mgsh.ru</t>
+          <t>https://sevastopol.lolapizza.ru</t>
         </is>
       </c>
       <c r="N133" s="44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> +7 (978) 723-98-80</t>
+          <t xml:space="preserve">
+8 (800) 500-99-29</t>
         </is>
       </c>
       <c r="O133" s="35" t="inlineStr">
         <is>
-          <t>ежедневно 10:00-22:00</t>
+          <t>ежедневно 09:00–22:00</t>
         </is>
       </c>
       <c r="P133" s="35" t="inlineStr">
@@ -9564,71 +9564,71 @@
     <row r="134" ht="15.75" customHeight="1" s="45">
       <c r="A134" s="34" t="inlineStr">
         <is>
-          <t>Кафе</t>
+          <t>Доставки</t>
         </is>
       </c>
       <c r="B134" s="34" t="inlineStr">
         <is>
-          <t>Пиццерии</t>
+          <t>Фастфуд</t>
         </is>
       </c>
       <c r="C134" s="34" t="inlineStr">
         <is>
-          <t>Лола Пицца</t>
+          <t>Вкусный Маяк</t>
         </is>
       </c>
       <c r="D134" s="37" t="inlineStr">
         <is>
-          <t>✔️ Пиццерия на Октябрьской Революции
-✔️ Большой выбор пицц, быстрая доставка</t>
+          <t>✔️ Шаурма, бургеры, сэндвичи, десерты и «супы дня» с новым вкусом каждый день.
+✔️ Быстро и вкусно, акции</t>
         </is>
       </c>
       <c r="E134" s="37" t="n"/>
       <c r="F134" s="34" t="inlineStr">
         <is>
-          <t>проспект Октябрьской Революции, 24</t>
+          <t>Фиолентовское шоссе, 1/10</t>
         </is>
       </c>
       <c r="G134" s="34" t="inlineStr">
         <is>
-          <t>Лётчики</t>
+          <t>5-й км</t>
         </is>
       </c>
       <c r="H134" s="34" t="inlineStr">
         <is>
-          <t>44.592218, 33.455635</t>
-        </is>
-      </c>
-      <c r="I134" s="38" t="inlineStr">
-        <is>
-          <t>https://avatars.mds.yandex.net/get-altay/11419181/2a00000194b2e38ed36d35839e69b9c375ae/XXXL</t>
-        </is>
-      </c>
-      <c r="J134" s="30" t="inlineStr">
+          <t>44.583887, 33.483052</t>
+        </is>
+      </c>
+      <c r="I134" s="32" t="inlineStr">
+        <is>
+          <t>https://avatars.mds.yandex.net/get-altay/16503558/2a000001999bd48aa70932e4a1bc55287de7/XXXL</t>
+        </is>
+      </c>
+      <c r="J134" s="41" t="inlineStr">
         <is>
           <t>https://vk.ru/lolapizza_sev</t>
         </is>
       </c>
       <c r="K134" s="30" t="inlineStr">
         <is>
-          <t>https://t.me/lolapizza_podslushano</t>
+          <t>https://t.me/VkusnyyMayak</t>
         </is>
       </c>
       <c r="L134" s="35" t="n"/>
-      <c r="M134" s="29" t="inlineStr">
-        <is>
-          <t>https://sevastopol.lolapizza.ru</t>
+      <c r="M134" s="35" t="inlineStr">
+        <is>
+          <t>http://sevastopol.lolapizza.ru/</t>
         </is>
       </c>
       <c r="N134" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">
-8 (800) 500-99-29</t>
+ +7 (978) 291-09-01</t>
         </is>
       </c>
       <c r="O134" s="35" t="inlineStr">
         <is>
-          <t>ежедневно 09:00–22:00</t>
+          <t>ежедневно 09:00-18:00</t>
         </is>
       </c>
       <c r="P134" s="35" t="inlineStr">
@@ -9645,63 +9645,70 @@
       </c>
       <c r="B135" s="34" t="inlineStr">
         <is>
-          <t>Фастфуд</t>
+          <t>Суши и пицца</t>
         </is>
       </c>
       <c r="C135" s="34" t="inlineStr">
         <is>
-          <t>Вкусный Маяк</t>
+          <t>Манеки Неко</t>
         </is>
       </c>
       <c r="D135" s="37" t="inlineStr">
         <is>
-          <t>✔️ Шаурма, бургеры, сэндвичи, десерты и «супы дня» с новым вкусом каждый день.
-✔️ Быстро и вкусно, акции</t>
+          <t>✔️ Суши и пицца с доставкой
+✔️ Бонусы и кэшбек в приложении UDS, подарки именинникам</t>
         </is>
       </c>
       <c r="E135" s="37" t="n"/>
       <c r="F135" s="34" t="inlineStr">
         <is>
-          <t>Фиолентовское шоссе, 1/10</t>
+          <t>улица Гоголя, 36</t>
         </is>
       </c>
       <c r="G135" s="34" t="inlineStr">
         <is>
-          <t>5-й км</t>
+          <t>Центр</t>
         </is>
       </c>
       <c r="H135" s="34" t="inlineStr">
         <is>
-          <t>44.583887, 33.483052</t>
+          <t>44.588564, 33.516455</t>
         </is>
       </c>
       <c r="I135" s="32" t="inlineStr">
         <is>
-          <t>https://avatars.mds.yandex.net/get-altay/16503558/2a000001999bd48aa70932e4a1bc55287de7/XXXL</t>
-        </is>
-      </c>
-      <c r="J135" s="41" t="n"/>
-      <c r="K135" s="30" t="inlineStr">
-        <is>
-          <t>https://t.me/VkusnyyMayak</t>
+          <t>https://avatars.mds.yandex.net/get-altay/14377326/2a0000019617779d51b19b4524b494e915ef/XXXL</t>
+        </is>
+      </c>
+      <c r="J135" s="30" t="inlineStr">
+        <is>
+          <t>https://vk.ru/manekinekosev</t>
+        </is>
+      </c>
+      <c r="K135" s="39" t="inlineStr">
+        <is>
+          <t>https://t.me/manekisev</t>
         </is>
       </c>
       <c r="L135" s="35" t="n"/>
-      <c r="M135" s="35" t="n"/>
+      <c r="M135" s="32" t="inlineStr">
+        <is>
+          <t>https://maneki-sev.ru/</t>
+        </is>
+      </c>
       <c r="N135" s="44" t="inlineStr">
         <is>
-          <t xml:space="preserve">
- +7 (978) 291-09-01</t>
+          <t xml:space="preserve"> +7 (978) 148-10-49</t>
         </is>
       </c>
       <c r="O135" s="35" t="inlineStr">
         <is>
-          <t>ежедневно 09:00-18:00</t>
+          <t>ежедневно 10:00–22:30</t>
         </is>
       </c>
       <c r="P135" s="35" t="inlineStr">
         <is>
-          <t>Быстрое питание</t>
+          <t>Доставка</t>
         </is>
       </c>
     </row>
@@ -9713,47 +9720,47 @@
       </c>
       <c r="B136" s="34" t="inlineStr">
         <is>
-          <t>Суши и пицца</t>
+          <t>Пицца и бургеры</t>
         </is>
       </c>
       <c r="C136" s="34" t="inlineStr">
         <is>
-          <t>Манеки Неко</t>
+          <t>Море Доставит</t>
         </is>
       </c>
       <c r="D136" s="37" t="inlineStr">
         <is>
-          <t>✔️ Суши и пицца с доставкой
-✔️ Бонусы и кэшбек в приложении UDS, подарки именинникам</t>
+          <t>✔️ Доставка пиццы и бургеров
+✔️ Пицца «Карбонара» с нежным тестом, привозят горячим</t>
         </is>
       </c>
       <c r="E136" s="37" t="n"/>
       <c r="F136" s="34" t="inlineStr">
         <is>
-          <t>улица Гоголя, 36</t>
+          <t>Казачья улица, 60, корп. 9</t>
         </is>
       </c>
       <c r="G136" s="34" t="inlineStr">
         <is>
-          <t>Центр</t>
+          <t>Казачка</t>
         </is>
       </c>
       <c r="H136" s="34" t="inlineStr">
         <is>
-          <t>44.588564, 33.516455</t>
+          <t>44.561578, 33.419261</t>
         </is>
       </c>
       <c r="I136" s="32" t="inlineStr">
         <is>
-          <t>https://avatars.mds.yandex.net/get-altay/14377326/2a0000019617779d51b19b4524b494e915ef/XXXL</t>
+          <t>https://avatars.mds.yandex.net/get-altay/9114271/2a00000190732ff63394c253cf34514a7db0/XXXL</t>
         </is>
       </c>
       <c r="J136" s="30" t="inlineStr">
         <is>
-          <t>https://vk.ru/manekinekosev</t>
-        </is>
-      </c>
-      <c r="K136" s="39" t="inlineStr">
+          <t>https://vk.ru/more_dostavit</t>
+        </is>
+      </c>
+      <c r="K136" s="41" t="inlineStr">
         <is>
           <t>https://t.me/manekisev</t>
         </is>
@@ -9761,17 +9768,17 @@
       <c r="L136" s="35" t="n"/>
       <c r="M136" s="32" t="inlineStr">
         <is>
-          <t>https://maneki-sev.ru/</t>
+          <t>https://edamore.ru/</t>
         </is>
       </c>
       <c r="N136" s="44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> +7 (978) 148-10-49</t>
+          <t xml:space="preserve"> +7 (8692) 88-71-43</t>
         </is>
       </c>
       <c r="O136" s="35" t="inlineStr">
         <is>
-          <t>ежедневно 10:00–22:30</t>
+          <t>ежедневно 10:00-23:00</t>
         </is>
       </c>
       <c r="P136" s="35" t="inlineStr">
@@ -9783,66 +9790,66 @@
     <row r="137" ht="15.75" customHeight="1" s="45">
       <c r="A137" s="34" t="inlineStr">
         <is>
-          <t>Доставки</t>
+          <t>Пекарни</t>
         </is>
       </c>
       <c r="B137" s="34" t="inlineStr">
         <is>
-          <t>Пицца и бургеры</t>
+          <t>Пироги на заказ</t>
         </is>
       </c>
       <c r="C137" s="34" t="inlineStr">
         <is>
-          <t>Море Доставит</t>
+          <t>Студия вкуса Манако</t>
         </is>
       </c>
       <c r="D137" s="37" t="inlineStr">
         <is>
-          <t>✔️ Доставка пиццы и бургеров
-✔️ Пицца «Карбонара» с нежным тестом, привозят горячим</t>
+          <t>✔️ Кондитерская, торты на заказ
+✔️ Более 35 наименований, ежедневная доставка по городу</t>
         </is>
       </c>
       <c r="E137" s="37" t="n"/>
       <c r="F137" s="34" t="inlineStr">
         <is>
-          <t>Казачья улица, 60, корп. 9</t>
+          <t>Фиолентовское шоссе, 1/2</t>
         </is>
       </c>
       <c r="G137" s="34" t="inlineStr">
         <is>
-          <t>Казачка</t>
+          <t>Стрелка</t>
         </is>
       </c>
       <c r="H137" s="34" t="inlineStr">
         <is>
-          <t>44.561578, 33.419261</t>
+          <t>44.582132, 33.481296</t>
         </is>
       </c>
       <c r="I137" s="32" t="inlineStr">
         <is>
-          <t>https://avatars.mds.yandex.net/get-altay/9114271/2a00000190732ff63394c253cf34514a7db0/XXXL</t>
-        </is>
-      </c>
-      <c r="J137" s="30" t="inlineStr">
+          <t>https://avatars.mds.yandex.net/get-altay/7631654/2a000001841b227185dfc3bdff31c4ff260f/XXXL</t>
+        </is>
+      </c>
+      <c r="J137" s="41" t="inlineStr">
         <is>
           <t>https://vk.ru/more_dostavit</t>
         </is>
       </c>
       <c r="K137" s="41" t="n"/>
       <c r="L137" s="35" t="n"/>
-      <c r="M137" s="32" t="inlineStr">
+      <c r="M137" s="35" t="inlineStr">
         <is>
           <t>https://edamore.ru/</t>
         </is>
       </c>
       <c r="N137" s="44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> +7 (8692) 88-71-43</t>
+          <t xml:space="preserve"> +7 (989) 082-19-48</t>
         </is>
       </c>
       <c r="O137" s="35" t="inlineStr">
         <is>
-          <t>ежедневно 10:00-23:00</t>
+          <t>ежедневно 10:00-18:00</t>
         </is>
       </c>
       <c r="P137" s="35" t="inlineStr">
@@ -9859,58 +9866,66 @@
       </c>
       <c r="B138" s="34" t="inlineStr">
         <is>
-          <t>Пироги на заказ</t>
+          <t>Сеть пекарен</t>
         </is>
       </c>
       <c r="C138" s="34" t="inlineStr">
         <is>
-          <t>Студия вкуса Манако</t>
+          <t>Царь-хлеб</t>
         </is>
       </c>
       <c r="D138" s="37" t="inlineStr">
         <is>
-          <t>✔️ Кондитерская, торты на заказ
-✔️ Более 35 наименований, ежедневная доставка по городу</t>
+          <t>✔️ Сеть пекарен: свежий хлеб и большой ассортимент выпечки</t>
         </is>
       </c>
       <c r="E138" s="37" t="n"/>
       <c r="F138" s="34" t="inlineStr">
         <is>
-          <t>Фиолентовское шоссе, 1/2</t>
+          <t>улица Супруна, 21</t>
         </is>
       </c>
       <c r="G138" s="34" t="inlineStr">
         <is>
-          <t>Стрелка</t>
+          <t>Центр</t>
         </is>
       </c>
       <c r="H138" s="34" t="inlineStr">
         <is>
-          <t>44.582132, 33.481296</t>
+          <t>44.587882, 33.519057</t>
         </is>
       </c>
       <c r="I138" s="32" t="inlineStr">
         <is>
-          <t>https://avatars.mds.yandex.net/get-altay/7631654/2a000001841b227185dfc3bdff31c4ff260f/XXXL</t>
-        </is>
-      </c>
-      <c r="J138" s="41" t="n"/>
+          <t>https://avatars.mds.yandex.net/get-altay/4079915/2a00000179e7c16666d172bb183c39b71370/XXXL</t>
+        </is>
+      </c>
+      <c r="J138" s="30" t="inlineStr">
+        <is>
+          <t>https://vk.ru/tsar_hleb</t>
+        </is>
+      </c>
       <c r="K138" s="41" t="n"/>
       <c r="L138" s="35" t="n"/>
-      <c r="M138" s="35" t="n"/>
+      <c r="M138" s="32" t="inlineStr">
+        <is>
+          <t>https://www.tsarhleb.ru/</t>
+        </is>
+      </c>
       <c r="N138" s="44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> +7 (989) 082-19-48</t>
+          <t xml:space="preserve">
+ +7 (978) 987-10-09</t>
         </is>
       </c>
       <c r="O138" s="35" t="inlineStr">
         <is>
-          <t>ежедневно 10:00-18:00</t>
+          <t>пн-сб 07:00–19:00 вс 07:00–18:00</t>
         </is>
       </c>
       <c r="P138" s="35" t="inlineStr">
         <is>
-          <t>Доставка</t>
+          <t>Пекарня</t>
         </is>
       </c>
     </row>
@@ -9932,28 +9947,29 @@
       </c>
       <c r="D139" s="37" t="inlineStr">
         <is>
-          <t>✔️ Сеть пекарен: свежий хлеб и большой ассортимент выпечки</t>
+          <t>✔️ Пекарня на проспекте Победы
+✔️ Свежий хлеб с пылу с жару</t>
         </is>
       </c>
       <c r="E139" s="37" t="n"/>
       <c r="F139" s="34" t="inlineStr">
         <is>
-          <t>улица Супруна, 21</t>
+          <t>проспект Победы, 38В</t>
         </is>
       </c>
       <c r="G139" s="34" t="inlineStr">
         <is>
-          <t>Центр</t>
+          <t>Победа</t>
         </is>
       </c>
       <c r="H139" s="34" t="inlineStr">
         <is>
-          <t>44.587882, 33.519057</t>
+          <t>44.587349, 33.559646</t>
         </is>
       </c>
       <c r="I139" s="32" t="inlineStr">
         <is>
-          <t>https://avatars.mds.yandex.net/get-altay/4079915/2a00000179e7c16666d172bb183c39b71370/XXXL</t>
+          <t>https://avatars.mds.yandex.net/get-altay/1970665/2a00000170905ceabe55a80e8158f3f3f101/XXXL</t>
         </is>
       </c>
       <c r="J139" s="30" t="inlineStr">
@@ -9976,7 +9992,7 @@
       </c>
       <c r="O139" s="35" t="inlineStr">
         <is>
-          <t>пн-сб 07:00–19:00 вс 07:00–18:00</t>
+          <t>ежедневно 07:30–19:00</t>
         </is>
       </c>
       <c r="P139" s="35" t="inlineStr">
@@ -10003,29 +10019,29 @@
       </c>
       <c r="D140" s="37" t="inlineStr">
         <is>
-          <t>✔️ Пекарня на проспекте Победы
-✔️ Свежий хлеб с пылу с жару</t>
+          <t>✔️ Пекарня на Токарева
+✔️ Хлеб, пироговые, сладости</t>
         </is>
       </c>
       <c r="E140" s="37" t="n"/>
       <c r="F140" s="34" t="inlineStr">
         <is>
-          <t>проспект Победы, 38В</t>
+          <t>улица Токарева, 2В</t>
         </is>
       </c>
       <c r="G140" s="34" t="inlineStr">
         <is>
-          <t>Победа</t>
+          <t>Остряки</t>
         </is>
       </c>
       <c r="H140" s="34" t="inlineStr">
         <is>
-          <t>44.587349, 33.559646</t>
+          <t>44.582280, 33.503900</t>
         </is>
       </c>
       <c r="I140" s="32" t="inlineStr">
         <is>
-          <t>https://avatars.mds.yandex.net/get-altay/1970665/2a00000170905ceabe55a80e8158f3f3f101/XXXL</t>
+          <t>https://avatars.mds.yandex.net/get-altay/2044663/2a0000016f40f94e611a578833631de543b6/XXXL</t>
         </is>
       </c>
       <c r="J140" s="30" t="inlineStr">
@@ -10065,62 +10081,61 @@
       </c>
       <c r="B141" s="34" t="inlineStr">
         <is>
-          <t>Сеть пекарен</t>
+          <t>Осетинские пироги</t>
         </is>
       </c>
       <c r="C141" s="34" t="inlineStr">
         <is>
-          <t>Царь-хлеб</t>
+          <t>Kurtat</t>
         </is>
       </c>
       <c r="D141" s="37" t="inlineStr">
         <is>
-          <t>✔️ Пекарня на Токарева
-✔️ Хлеб, пироговые, сладости</t>
+          <t>✔️ Осетинские пироги с доставкой
+✔️ Сочный мясной фыдджын, горячие прямо из печи</t>
         </is>
       </c>
       <c r="E141" s="37" t="n"/>
       <c r="F141" s="34" t="inlineStr">
         <is>
-          <t>улица Токарева, 2В</t>
+          <t>улица Тараса Шевченко, 46</t>
         </is>
       </c>
       <c r="G141" s="34" t="inlineStr">
         <is>
-          <t>Остряки</t>
+          <t>Омега</t>
         </is>
       </c>
       <c r="H141" s="34" t="inlineStr">
         <is>
-          <t>44.582280, 33.503900</t>
-        </is>
-      </c>
-      <c r="I141" s="32" t="inlineStr">
-        <is>
-          <t>https://avatars.mds.yandex.net/get-altay/2044663/2a0000016f40f94e611a578833631de543b6/XXXL</t>
+          <t>44.573311, 33.457525</t>
+        </is>
+      </c>
+      <c r="I141" s="38" t="inlineStr">
+        <is>
+          <t>https://sun9-7.vkuserphoto.ru/s/v1/ig1/JJ6WsOoD6Nag6U7Ek4R8OL1iOXq74l_MORScR9a4wxbszuk4GTqvOVzAbdhuouuB0cW3XyXO4PIp9Q.jpg?quality=96&amp;as=32x23,48x35,72x53,108x79,160x117,240x175,360x263,480x350,540x394,640x467,720x525,1080x788,1239x904&amp;from=bu&amp;cs=1239x0</t>
         </is>
       </c>
       <c r="J141" s="30" t="inlineStr">
         <is>
-          <t>https://vk.ru/tsar_hleb</t>
+          <t>https://vk.ru/club28413298</t>
         </is>
       </c>
       <c r="K141" s="41" t="n"/>
       <c r="L141" s="35" t="n"/>
       <c r="M141" s="32" t="inlineStr">
         <is>
-          <t>https://www.tsarhleb.ru/</t>
+          <t>https://pirogi-kurtat.ru/</t>
         </is>
       </c>
       <c r="N141" s="44" t="inlineStr">
         <is>
-          <t xml:space="preserve">
- +7 (978) 987-10-09</t>
+          <t xml:space="preserve"> +7 (978) 749-97-18</t>
         </is>
       </c>
       <c r="O141" s="35" t="inlineStr">
         <is>
-          <t>ежедневно 07:30–19:00</t>
+          <t>ежедневно 09:00–19:30</t>
         </is>
       </c>
       <c r="P141" s="35" t="inlineStr">
@@ -10135,63 +10150,58 @@
           <t>Пекарни</t>
         </is>
       </c>
-      <c r="B142" s="34" t="inlineStr">
-        <is>
-          <t>Осетинские пироги</t>
-        </is>
-      </c>
       <c r="C142" s="34" t="inlineStr">
         <is>
-          <t>Kurtat</t>
+          <t>Из печи</t>
         </is>
       </c>
       <c r="D142" s="37" t="inlineStr">
         <is>
-          <t>✔️ Осетинские пироги с доставкой
-✔️ Сочный мясной фыдджын, горячие прямо из печи</t>
+          <t>✔️ Пекарня на Северной стороне
+✔️ Свежие элеши, ассортимент меняется</t>
         </is>
       </c>
       <c r="E142" s="37" t="n"/>
       <c r="F142" s="34" t="inlineStr">
         <is>
-          <t>улица Тараса Шевченко, 46</t>
+          <t>улица Челюскинцев, 57/3</t>
         </is>
       </c>
       <c r="G142" s="34" t="inlineStr">
         <is>
-          <t>Омега</t>
+          <t>Северная</t>
         </is>
       </c>
       <c r="H142" s="34" t="inlineStr">
         <is>
-          <t>44.573311, 33.457525</t>
-        </is>
-      </c>
-      <c r="I142" s="38" t="inlineStr">
+          <t>44.639028, 33.539508</t>
+        </is>
+      </c>
+      <c r="I142" s="35" t="inlineStr">
         <is>
           <t>https://sun9-7.vkuserphoto.ru/s/v1/ig1/JJ6WsOoD6Nag6U7Ek4R8OL1iOXq74l_MORScR9a4wxbszuk4GTqvOVzAbdhuouuB0cW3XyXO4PIp9Q.jpg?quality=96&amp;as=32x23,48x35,72x53,108x79,160x117,240x175,360x263,480x350,540x394,640x467,720x525,1080x788,1239x904&amp;from=bu&amp;cs=1239x0</t>
         </is>
       </c>
-      <c r="J142" s="30" t="inlineStr">
+      <c r="J142" s="41" t="inlineStr">
         <is>
           <t>https://vk.ru/club28413298</t>
         </is>
       </c>
       <c r="K142" s="41" t="n"/>
       <c r="L142" s="35" t="n"/>
-      <c r="M142" s="32" t="inlineStr">
+      <c r="M142" s="35" t="inlineStr">
         <is>
           <t>https://pirogi-kurtat.ru/</t>
         </is>
       </c>
       <c r="N142" s="44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> +7 (978) 749-97-18</t>
+          <t xml:space="preserve"> +7 (978) 592-25-77</t>
         </is>
       </c>
       <c r="O142" s="35" t="inlineStr">
         <is>
-          <t>ежедневно 09:00–19:30</t>
+          <t>ежедневно 08:00–18:00</t>
         </is>
       </c>
       <c r="P142" s="35" t="inlineStr">
@@ -10203,24 +10213,24 @@
     <row r="143" ht="15.75" customHeight="1" s="45">
       <c r="A143" s="34" t="inlineStr">
         <is>
-          <t>Пекарни</t>
+          <t>Кофе</t>
         </is>
       </c>
       <c r="C143" s="34" t="inlineStr">
         <is>
-          <t>Из печи</t>
+          <t>Добро Кофе</t>
         </is>
       </c>
       <c r="D143" s="37" t="inlineStr">
         <is>
-          <t>✔️ Пекарня на Северной стороне
-✔️ Свежие элеши, ассортимент меняется</t>
+          <t>✔️ Кофейня на площади Захарова (Северная)
+✔️ Вкусный кофе и свежие булочки, необычный интерьер</t>
         </is>
       </c>
       <c r="E143" s="37" t="n"/>
       <c r="F143" s="34" t="inlineStr">
         <is>
-          <t>улица Челюскинцев, 57/3</t>
+          <t>площадь Генерала Захарова, 5</t>
         </is>
       </c>
       <c r="G143" s="34" t="inlineStr">
@@ -10230,70 +10240,87 @@
       </c>
       <c r="H143" s="34" t="inlineStr">
         <is>
-          <t>44.639028, 33.539508</t>
-        </is>
-      </c>
-      <c r="I143" s="35" t="n"/>
+          <t>44.627436, 33.536556</t>
+        </is>
+      </c>
+      <c r="I143" s="32" t="inlineStr">
+        <is>
+          <t>https://avatars.mds.yandex.net/get-altay/14907397/2a0000019a8b810bd700d6f03f7b589e7ee1/XXXL</t>
+        </is>
+      </c>
       <c r="J143" s="41" t="n"/>
-      <c r="K143" s="41" t="n"/>
+      <c r="K143" s="30" t="inlineStr">
+        <is>
+          <t>https://t.me/dobrocoffeeSev_bot</t>
+        </is>
+      </c>
       <c r="L143" s="35" t="n"/>
       <c r="M143" s="35" t="n"/>
       <c r="N143" s="44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> +7 (978) 592-25-77</t>
+          <t xml:space="preserve"> +7 (978) 896-52-58</t>
         </is>
       </c>
       <c r="O143" s="35" t="inlineStr">
         <is>
-          <t>ежедневно 08:00–18:00</t>
+          <t>ежедневно 08:00–20:00</t>
         </is>
       </c>
       <c r="P143" s="35" t="inlineStr">
         <is>
-          <t>Пекарня</t>
+          <t>Кофе</t>
         </is>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1" s="45">
       <c r="A144" s="34" t="inlineStr">
         <is>
-          <t>Кофе</t>
+          <t>Рестораны</t>
+        </is>
+      </c>
+      <c r="B144" s="34" t="inlineStr">
+        <is>
+          <t>Восточная кухня</t>
         </is>
       </c>
       <c r="C144" s="34" t="inlineStr">
         <is>
-          <t>Добро Кофе</t>
+          <t>Мзиури</t>
         </is>
       </c>
       <c r="D144" s="37" t="inlineStr">
         <is>
-          <t>✔️ Кофейня на площади Захарова (Северная)
-✔️ Вкусный кофе и свежие булочки, необычный интерьер</t>
+          <t>✔️ Ресторан восточной кухни на Вакуленчука
+✔️ Шашлык, люля, хачапури</t>
         </is>
       </c>
       <c r="E144" s="37" t="n"/>
       <c r="F144" s="34" t="inlineStr">
         <is>
-          <t>площадь Генерала Захарова, 5</t>
+          <t>улица Вакуленчука, 39</t>
         </is>
       </c>
       <c r="G144" s="34" t="inlineStr">
         <is>
-          <t>Северная</t>
+          <t>Стрелка</t>
         </is>
       </c>
       <c r="H144" s="34" t="inlineStr">
         <is>
-          <t>44.627436, 33.536556</t>
+          <t>44.586703, 33.478639</t>
         </is>
       </c>
       <c r="I144" s="32" t="inlineStr">
         <is>
-          <t>https://avatars.mds.yandex.net/get-altay/14907397/2a0000019a8b810bd700d6f03f7b589e7ee1/XXXL</t>
-        </is>
-      </c>
-      <c r="J144" s="41" t="n"/>
-      <c r="K144" s="30" t="inlineStr">
+          <t>https://avatars.mds.yandex.net/get-altay/6143287/2a000001848a95e86d45d03a950c45929cd3/XXXL</t>
+        </is>
+      </c>
+      <c r="J144" s="30" t="inlineStr">
+        <is>
+          <t>https://vk.ru/restoran_mziuri</t>
+        </is>
+      </c>
+      <c r="K144" s="41" t="inlineStr">
         <is>
           <t>https://t.me/dobrocoffeeSev_bot</t>
         </is>
@@ -10302,17 +10329,17 @@
       <c r="M144" s="35" t="n"/>
       <c r="N144" s="44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> +7 (978) 896-52-58</t>
+          <t xml:space="preserve"> +7 (978) 793-00-61</t>
         </is>
       </c>
       <c r="O144" s="35" t="inlineStr">
         <is>
-          <t>ежедневно 08:00–20:00</t>
+          <t>вт-вс 12:00–00:00</t>
         </is>
       </c>
       <c r="P144" s="35" t="inlineStr">
         <is>
-          <t>Кофе</t>
+          <t>Кафе</t>
         </is>
       </c>
     </row>
@@ -10322,46 +10349,41 @@
           <t>Рестораны</t>
         </is>
       </c>
-      <c r="B145" s="34" t="inlineStr">
-        <is>
-          <t>Восточная кухня</t>
-        </is>
-      </c>
       <c r="C145" s="34" t="inlineStr">
         <is>
-          <t>Мзиури</t>
+          <t>Рататуй</t>
         </is>
       </c>
       <c r="D145" s="37" t="inlineStr">
         <is>
-          <t>✔️ Ресторан восточной кухни на Вакуленчука
-✔️ Шашлык, люля, хачапури</t>
+          <t>✔️ Столовая на Большой Морской
+✔️ Место, где вы можете вкусно и сытно поесть по доступным ценам.</t>
         </is>
       </c>
       <c r="E145" s="37" t="n"/>
       <c r="F145" s="34" t="inlineStr">
         <is>
-          <t>улица Вакуленчука, 39</t>
+          <t>Большая Морская, 52/2</t>
         </is>
       </c>
       <c r="G145" s="34" t="inlineStr">
         <is>
-          <t>Стрелка</t>
+          <t>Центр</t>
         </is>
       </c>
       <c r="H145" s="34" t="inlineStr">
         <is>
-          <t>44.586703, 33.478639</t>
+          <t>44.602031, 33.523361</t>
         </is>
       </c>
       <c r="I145" s="32" t="inlineStr">
         <is>
-          <t>https://avatars.mds.yandex.net/get-altay/6143287/2a000001848a95e86d45d03a950c45929cd3/XXXL</t>
+          <t>https://avatars.mds.yandex.net/get-altay/5236391/2a0000017b637e1cc032c70d426f75578c97/XXXL</t>
         </is>
       </c>
       <c r="J145" s="30" t="inlineStr">
         <is>
-          <t>https://vk.ru/restoran_mziuri</t>
+          <t>https://vk.ru/rataty_dining.room</t>
         </is>
       </c>
       <c r="K145" s="41" t="n"/>
@@ -10369,61 +10391,61 @@
       <c r="M145" s="35" t="n"/>
       <c r="N145" s="44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> +7 (978) 793-00-61</t>
+          <t xml:space="preserve"> +7 (978) 842-82-30</t>
         </is>
       </c>
       <c r="O145" s="35" t="inlineStr">
         <is>
-          <t>вт-вс 12:00–00:00</t>
+          <t>ежедневно 09:30–21:00</t>
         </is>
       </c>
       <c r="P145" s="35" t="inlineStr">
         <is>
-          <t>Кафе</t>
+          <t>Столовая</t>
         </is>
       </c>
     </row>
     <row r="146" ht="15.75" customHeight="1" s="45">
       <c r="A146" s="34" t="inlineStr">
         <is>
-          <t>Рестораны</t>
+          <t>Кафе</t>
         </is>
       </c>
       <c r="C146" s="34" t="inlineStr">
         <is>
-          <t>Рататуй</t>
+          <t>Бульон</t>
         </is>
       </c>
       <c r="D146" s="37" t="inlineStr">
         <is>
-          <t>✔️ Столовая на Большой Морской
-✔️ Место, где вы можете вкусно и сытно поесть по доступным ценам.</t>
+          <t>✔️ Столовая в ТЦ «Стрелецкий»
+✔️ Это место, где можно вкусно и сытно поесть по доступным ценам.</t>
         </is>
       </c>
       <c r="E146" s="37" t="n"/>
       <c r="F146" s="34" t="inlineStr">
         <is>
-          <t>Большая Морская, 52/2</t>
+          <t>проспект Гагарина, 8 (ТЦ «Стрелецкий»)</t>
         </is>
       </c>
       <c r="G146" s="34" t="inlineStr">
         <is>
-          <t>Центр</t>
+          <t>Стрелка</t>
         </is>
       </c>
       <c r="H146" s="34" t="inlineStr">
         <is>
-          <t>44.602031, 33.523361</t>
+          <t>44.599691, 33.489818</t>
         </is>
       </c>
       <c r="I146" s="32" t="inlineStr">
         <is>
-          <t>https://avatars.mds.yandex.net/get-altay/5236391/2a0000017b637e1cc032c70d426f75578c97/XXXL</t>
+          <t>https://avatars.mds.yandex.net/get-altay/14021276/2a00000192d7917fafee5d32fe97d4c3cb75/XXXL</t>
         </is>
       </c>
       <c r="J146" s="30" t="inlineStr">
         <is>
-          <t>https://vk.ru/rataty_dining.room</t>
+          <t>https://vk.ru/bylionsev</t>
         </is>
       </c>
       <c r="K146" s="41" t="n"/>
@@ -10431,12 +10453,13 @@
       <c r="M146" s="35" t="n"/>
       <c r="N146" s="44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> +7 (978) 842-82-30</t>
+          <t xml:space="preserve"> 
++7 (978) 859-04-89</t>
         </is>
       </c>
       <c r="O146" s="35" t="inlineStr">
         <is>
-          <t>ежедневно 09:30–21:00</t>
+          <t>ежедневно 09:00–21:00</t>
         </is>
       </c>
       <c r="P146" s="35" t="inlineStr">
@@ -10446,44 +10469,18 @@
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1" s="45">
-      <c r="A147" s="34" t="inlineStr">
-        <is>
-          <t>Кафе</t>
-        </is>
-      </c>
-      <c r="C147" s="34" t="inlineStr">
-        <is>
-          <t>Бульон</t>
-        </is>
-      </c>
-      <c r="D147" s="37" t="inlineStr">
-        <is>
-          <t>✔️ Столовая в ТЦ «Стрелецкий»
-✔️ Это место, где можно вкусно и сытно поесть по доступным ценам.</t>
-        </is>
-      </c>
+      <c r="A147" s="35" t="n"/>
+      <c r="D147" s="37" t="n"/>
       <c r="E147" s="37" t="n"/>
-      <c r="F147" s="34" t="inlineStr">
-        <is>
-          <t>проспект Гагарина, 8 (ТЦ «Стрелецкий»)</t>
-        </is>
-      </c>
-      <c r="G147" s="34" t="inlineStr">
-        <is>
-          <t>Стрелка</t>
-        </is>
-      </c>
-      <c r="H147" s="34" t="inlineStr">
-        <is>
-          <t>44.599691, 33.489818</t>
-        </is>
-      </c>
-      <c r="I147" s="32" t="inlineStr">
+      <c r="F147" s="35" t="n"/>
+      <c r="G147" s="35" t="n"/>
+      <c r="H147" s="35" t="n"/>
+      <c r="I147" s="35" t="inlineStr">
         <is>
           <t>https://avatars.mds.yandex.net/get-altay/14021276/2a00000192d7917fafee5d32fe97d4c3cb75/XXXL</t>
         </is>
       </c>
-      <c r="J147" s="30" t="inlineStr">
+      <c r="J147" s="41" t="inlineStr">
         <is>
           <t>https://vk.ru/bylionsev</t>
         </is>
@@ -10491,22 +10488,9 @@
       <c r="K147" s="41" t="n"/>
       <c r="L147" s="35" t="n"/>
       <c r="M147" s="35" t="n"/>
-      <c r="N147" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 
-+7 (978) 859-04-89</t>
-        </is>
-      </c>
-      <c r="O147" s="35" t="inlineStr">
-        <is>
-          <t>ежедневно 09:00–21:00</t>
-        </is>
-      </c>
-      <c r="P147" s="35" t="inlineStr">
-        <is>
-          <t>Столовая</t>
-        </is>
-      </c>
+      <c r="N147" s="44" t="n"/>
+      <c r="O147" s="35" t="n"/>
+      <c r="P147" s="35" t="n"/>
     </row>
     <row r="148" ht="15.75" customHeight="1" s="45">
       <c r="A148" s="35" t="n"/>
@@ -13694,17 +13678,16 @@
     </row>
     <row r="347" ht="15.75" customHeight="1" s="45">
       <c r="A347" s="35" t="n"/>
-      <c r="D347" s="37" t="n"/>
-      <c r="E347" s="37" t="n"/>
+      <c r="E347" s="35" t="n"/>
       <c r="F347" s="35" t="n"/>
       <c r="G347" s="35" t="n"/>
       <c r="H347" s="35" t="n"/>
       <c r="I347" s="35" t="n"/>
-      <c r="J347" s="41" t="n"/>
-      <c r="K347" s="41" t="n"/>
+      <c r="J347" s="35" t="n"/>
+      <c r="K347" s="35" t="n"/>
       <c r="L347" s="35" t="n"/>
       <c r="M347" s="35" t="n"/>
-      <c r="N347" s="44" t="n"/>
+      <c r="N347" s="35" t="n"/>
       <c r="O347" s="35" t="n"/>
       <c r="P347" s="35" t="n"/>
     </row>
@@ -23248,21 +23231,7 @@
       <c r="O983" s="35" t="n"/>
       <c r="P983" s="35" t="n"/>
     </row>
-    <row r="984" ht="15.75" customHeight="1" s="45">
-      <c r="A984" s="35" t="n"/>
-      <c r="E984" s="35" t="n"/>
-      <c r="F984" s="35" t="n"/>
-      <c r="G984" s="35" t="n"/>
-      <c r="H984" s="35" t="n"/>
-      <c r="I984" s="35" t="n"/>
-      <c r="J984" s="35" t="n"/>
-      <c r="K984" s="35" t="n"/>
-      <c r="L984" s="35" t="n"/>
-      <c r="M984" s="35" t="n"/>
-      <c r="N984" s="35" t="n"/>
-      <c r="O984" s="35" t="n"/>
-      <c r="P984" s="35" t="n"/>
-    </row>
+    <row r="984" ht="15.75" customHeight="1" s="45"/>
   </sheetData>
   <mergeCells count="44">
     <mergeCell ref="D20:E20"/>
@@ -23693,51 +23662,47 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J130" r:id="rId380"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId381"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J131" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J132" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J133" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J134" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J136" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M137" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J139" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M139" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J140" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M140" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J141" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J142" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J145" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J146" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J147" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J132" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J133" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J134" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J136" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M137" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J139" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M139" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J140" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M140" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J141" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J142" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J145" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J146" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J147" r:id="rId423"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -23820,11 +23785,7 @@
           <t>44.512959, 33.479362</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
-        <is>
-          <t>https://t.me/krym_crimea_rf/28133</t>
-        </is>
-      </c>
+      <c r="F2" s="9" t="n"/>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="45">
       <c r="A3" s="42" t="inlineStr">
@@ -23876,11 +23837,7 @@
           <t>44.503483, 33.507114</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>https://t.me/krym_crimea_rf/28788</t>
-        </is>
-      </c>
+      <c r="F5" s="9" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1" s="45">
       <c r="A6" s="42" t="inlineStr">
@@ -23972,11 +23929,7 @@
           <t>44.468725, 33.637842</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>https://t.me/krym_crimea_rf/26313</t>
-        </is>
-      </c>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1" s="45">
       <c r="A9" s="42" t="inlineStr">
@@ -24004,11 +23957,7 @@
           <t>44.521853, 33.468460</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>https://t.me/krym_crimea_rf/20880</t>
-        </is>
-      </c>
+      <c r="F9" s="9" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1" s="45">
       <c r="A10" s="42" t="inlineStr">
@@ -24159,11 +24108,7 @@
           <t>44.502228, 33.493548</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>https://t.me/prokrum/9208</t>
-        </is>
-      </c>
+      <c r="F14" s="9" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="45">
       <c r="A15" s="42" t="inlineStr">
@@ -31965,15 +31910,10 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
